--- a/kanade/financial-model-jp.xlsx
+++ b/kanade/financial-model-jp.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="295">
   <si>
     <r>
       <rPr>
@@ -557,7 +557,139 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">手数料。分配プールはこの「純売上」に対して </t>
+      <t xml:space="preserve">手数料。分配プールはこの「純売上」に対する比率（設計書 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">08 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と同じ定義）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・分配率は固定ではなく段階制（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30% → 45%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。月次予測シートは店舗数から自動判定し、一度上がった段階は下がらない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・単位経済・損益分岐点シートは「現行段階の分配率」（前提条件 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）を使う。段階が進んだ場合はこの値を更新すること。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・分配率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">でも税込売上のうち手元に残る貢献利益は約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">57%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">では約 </t>
     </r>
     <r>
       <rPr>
@@ -574,10 +706,1060 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（設計書 </t>
-    </r>
-    <r>
-      <rPr>
+      <t xml:space="preserve">。この構造が損益分岐点を大きく左右する。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">・創作者への分配は商用再生のみが対象。リスナー向け無料ストリーミングは分配対象外。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・インフラ費は </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（エグレス無料）前提。帯域費をゼロとしているのはこのため。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">・人件費は日本の相場を仮置きしたもの。実際の採用計画に合わせて必ず調整すること。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出典</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JASRAC BGM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使用料（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">㎡以下 年額 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">¥6,000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ほか面積区分）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: JASRAC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公式 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FAQ / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使用料規程 第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BGM</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">USEN MUSIC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月額 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">¥6,600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜・初期費用 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">¥22,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33,000: USEN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公式および代理店公開情報（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月時点）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・モンスター・チャンネル </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">¥1,880</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,880</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（税抜）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: monstar.ch </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公式料金ページ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月時点）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・その他 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BGM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">サービス料金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">店舗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BGM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">サービス比較記事（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年版）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・レコード演奏・伝達権</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日成立・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日公布、施行は公布から</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年以内</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Stripe </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手数料率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.6%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（日本国内カード）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: Stripe </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公開価格</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・上記以外の数値（成長率・解約率・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CAC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・人件費）は仮置き。実測値で置き換えること。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">本モデルは事業計画の検討用であり、会計・税務・法務上の助言ではありません。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">青字・黄色背景のセルのみ編集する。</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列は参考値（モデルは </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列のみを読む）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在値</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保守</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基本</t>
+  </si>
+  <si>
+    <t xml:space="preserve">楽観</t>
+  </si>
+  <si>
+    <t xml:space="preserve">備考</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">価格（税込）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Standard </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月額</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設計書 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の想定価格</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Custom </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月額</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">店舗専属カタログ・多店舗管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年払い割引率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年払い顧客に適用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年払い顧客比率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高いほど解約率が下がるが売上は減る</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顧客構成</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Standard </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">残りが </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Custom</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">収益構造</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">消費税率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総額表示のため税込価格から控除</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Stripe </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手数料率</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">日本国内カード。税込金額に対して課金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">創作者分配プール率（現行段階）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">単位経済・損益分岐点シートが使う値。月次予測は下の段階表で自動判定</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C-2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段階的分配率（設計書 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="0"/>
@@ -587,1093 +1769,149 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">と同じ定義）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・つまり税込売上のうち手元に残る貢献利益は約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">48%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。この構造が損益分岐点を大きく左右する。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">・創作者への分配は商用再生のみが対象。リスナー向け無料ストリーミングは分配対象外。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・インフラ費は </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">R2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（エグレス無料）前提。帯域費をゼロとしているのはこのため。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">・人件費は日本の相場を仮置きしたもの。実際の採用計画に合わせて必ず調整すること。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">出典</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JASRAC BGM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">使用料（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">500</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㎡以下 年額 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">¥6,000 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ほか面積区分）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: JASRAC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FAQ / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">使用料規程 第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">節 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BGM</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">USEN MUSIC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月額 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">¥6,600</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜・初期費用 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">¥22,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">33,000: USEN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式および代理店公開情報（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月時点）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・モンスター・チャンネル </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">¥1,880</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2,880</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（税抜）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: monstar.ch </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式料金ページ（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月時点）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・その他 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BGM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">サービス料金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">店舗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BGM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">サービス比較記事（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年版）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・レコード演奏・伝達権</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日成立・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">24</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日公布、施行は公布から</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年以内</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Stripe </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手数料率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3.6%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（日本国内カード）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: Stripe </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公開価格</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・上記以外の数値（成長率・解約率・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CAC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・人件費）は仮置き。実測値で置き換えること。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">本モデルは事業計画の検討用であり、会計・税務・法務上の助言ではありません。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">青字・黄色背景のセルのみ編集する。</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">F</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列は参考値（モデルは </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列のみを読む）。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">項目</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在値</t>
-  </si>
-  <si>
-    <t xml:space="preserve">保守</t>
-  </si>
-  <si>
-    <t xml:space="preserve">基本</t>
-  </si>
-  <si>
-    <t xml:space="preserve">楽観</t>
-  </si>
-  <si>
-    <t xml:space="preserve">備考</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A. </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">価格（税込）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Standard </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月額</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">設計書 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">01 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の想定価格</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Custom </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月額</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">店舗専属カタログ・多店舗管理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">年払い割引率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">年払い顧客に適用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">年払い顧客比率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高いほど解約率が下がるが売上は減る</t>
-  </si>
-  <si>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.2 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顧客構成</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Standard </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">比率</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">残りが </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Custom</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C. </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">収益構造</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">消費税率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">総額表示のため税込価格から控除</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Stripe </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手数料率</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">日本国内カード。税込金額に対して課金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">創作者分配プール率</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">純売上に対する比率（設計書 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">08</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF666666"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">立ち上げ期の上限店舗数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">この店舗数までは第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段階</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　同・分配率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成長期の上限店舗数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拡大期の上限店舗数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成熟期の分配率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">店以上</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">※ ラチェット式：一度到達した段階は店舗数が減っても下がらない。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ 段階制の運用ルールは設計書 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">08 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節を参照（初日公表・遡及変更なし）。</t>
     </r>
   </si>
   <si>
@@ -3310,6 +3548,9 @@
   </si>
   <si>
     <t xml:space="preserve">消費税</t>
+  </si>
+  <si>
+    <t xml:space="preserve">分配率（段階判定）</t>
   </si>
   <si>
     <t xml:space="preserve">創作者分配</t>
@@ -5299,7 +5540,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5513,6 +5754,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5852,7 +6097,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C34"/>
+  <dimension ref="B2:C36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -5982,18 +6227,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
+    <row r="24" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C24" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C26" s="8" t="s">
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C25" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C27" s="8" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6022,9 +6267,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="9" t="s">
+    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C33" s="8" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C34" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C36" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -6043,7 +6298,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G53"/>
+  <dimension ref="B2:G64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -6060,32 +6315,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -6095,7 +6350,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C7" s="15" t="n">
         <v>1980</v>
@@ -6110,12 +6365,12 @@
         <v>2980</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C8" s="15" t="n">
         <v>4980</v>
@@ -6130,12 +6385,12 @@
         <v>6980</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>0.2</v>
@@ -6150,12 +6405,12 @@
         <v>0.15</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>0.3</v>
@@ -6170,12 +6425,12 @@
         <v>0.5</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -6185,7 +6440,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>0.85</v>
@@ -6200,12 +6455,12 @@
         <v>0.75</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -6215,7 +6470,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C16" s="18" t="n">
         <v>0.1</v>
@@ -6230,12 +6485,12 @@
         <v>0.1</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C17" s="20" t="n">
         <v>0.036</v>
@@ -6250,32 +6505,32 @@
         <v>0.036</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="D18" s="19" t="n">
         <v>0.45</v>
       </c>
       <c r="E18" s="19" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="F18" s="19" t="n">
         <v>0.3</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -6285,489 +6540,639 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C21" s="22" t="n">
-        <v>5</v>
+        <v>499</v>
       </c>
       <c r="D21" s="23" t="n">
-        <v>3</v>
+        <v>499</v>
       </c>
       <c r="E21" s="23" t="n">
-        <v>5</v>
+        <v>499</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>65</v>
+        <v>499</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="D22" s="19" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="E22" s="19" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="F22" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>67</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="G22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>120</v>
+        <v>1499</v>
       </c>
       <c r="D23" s="23" t="n">
-        <v>60</v>
+        <v>1499</v>
       </c>
       <c r="E23" s="23" t="n">
-        <v>120</v>
+        <v>1499</v>
       </c>
       <c r="F23" s="23" t="n">
-        <v>250</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>69</v>
-      </c>
+        <v>1499</v>
+      </c>
+      <c r="G23" s="17"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G24" s="17"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D24" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E24" s="21" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F24" s="21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G24" s="17" t="s">
+      <c r="C25" s="22" t="n">
+        <v>2999</v>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>2999</v>
+      </c>
+      <c r="E25" s="23" t="n">
+        <v>2999</v>
+      </c>
+      <c r="F25" s="23" t="n">
+        <v>2999</v>
+      </c>
+      <c r="G25" s="17"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G26" s="17"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="5" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
+      <c r="C27" s="18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E27" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G27" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="6" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="15" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>35000</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G27" s="17" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" s="17"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="15" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>700000</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>700000</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>700000</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>78</v>
-      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C32" s="22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D32" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>80</v>
+        <v>10</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="15" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F33" s="16" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G33" s="17"/>
+        <v>78</v>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C34" s="22" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="E34" s="23" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="F34" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G35" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="15" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>300000</v>
-      </c>
-      <c r="G35" s="17"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="5" t="s">
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="23" t="n">
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="17"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" s="15" t="n">
-        <v>400000</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>400000</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>400000</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>400000</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C38" s="15" t="n">
-        <v>200000</v>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G38" s="17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C39" s="15" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G39" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
+      <c r="D41" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42" s="22" t="n">
-        <v>155</v>
-      </c>
-      <c r="D42" s="23" t="n">
-        <v>165</v>
-      </c>
-      <c r="E42" s="23" t="n">
-        <v>155</v>
-      </c>
-      <c r="F42" s="23" t="n">
-        <v>145</v>
-      </c>
-      <c r="G42" s="17"/>
+        <v>89</v>
+      </c>
+      <c r="C42" s="15" t="n">
+        <v>700000</v>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>700000</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>700000</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="25" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D43" s="26" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E43" s="26" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="F43" s="26" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G43" s="24" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="25" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="D44" s="26" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="E44" s="26" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="F44" s="26" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="G44" s="17" t="s">
-        <v>96</v>
-      </c>
+      <c r="C44" s="15" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F44" s="16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G44" s="17"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C45" s="22" t="n">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>3000</v>
+        <v>2</v>
       </c>
       <c r="E45" s="23" t="n">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="F45" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G45" s="24" t="s">
-        <v>98</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D46" s="23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E46" s="23" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F46" s="23" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G46" s="17" t="s">
-        <v>100</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="C46" s="15" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C47" s="27" t="n">
-        <v>140</v>
-      </c>
-      <c r="D47" s="28" t="n">
-        <v>140</v>
-      </c>
-      <c r="E47" s="28" t="n">
-        <v>140</v>
-      </c>
-      <c r="F47" s="28" t="n">
-        <v>140</v>
-      </c>
-      <c r="G47" s="24" t="s">
-        <v>102</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C47" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="17"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="15" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="15" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" s="15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="27" t="n">
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="22" t="n">
+        <v>155</v>
+      </c>
+      <c r="D53" s="23" t="n">
+        <v>165</v>
+      </c>
+      <c r="E53" s="23" t="n">
+        <v>155</v>
+      </c>
+      <c r="F53" s="23" t="n">
+        <v>145</v>
+      </c>
+      <c r="G53" s="17"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C54" s="25" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D54" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E54" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F54" s="26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G54" s="24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="25" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="D55" s="26" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="E55" s="26" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="F55" s="26" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E56" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F56" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D57" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F57" s="23" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G57" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C58" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="D58" s="28" t="n">
+        <v>140</v>
+      </c>
+      <c r="E58" s="28" t="n">
+        <v>140</v>
+      </c>
+      <c r="F58" s="28" t="n">
+        <v>140</v>
+      </c>
+      <c r="G58" s="24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C59" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="D48" s="28" t="n">
+      <c r="D59" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="E48" s="28" t="n">
+      <c r="E59" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="F48" s="28" t="n">
+      <c r="F59" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="G48" s="24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>111</v>
+      <c r="G59" s="24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -6797,34 +7202,34 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="10" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C6" s="32" t="n">
         <f aca="false">前提条件!$C$7</f>
@@ -6839,12 +7244,12 @@
         <v>2430</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C7" s="34" t="n">
         <f aca="false">前提条件!$C$7*(1-前提条件!$C$10*前提条件!$C$9)</f>
@@ -6859,12 +7264,12 @@
         <v>2284.2</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C8" s="34" t="n">
         <f aca="false">C7/(1+前提条件!$C$16)</f>
@@ -6879,12 +7284,12 @@
         <v>2076.54545454545</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C9" s="34" t="n">
         <f aca="false">-C7*前提条件!$C$17</f>
@@ -6899,12 +7304,12 @@
         <v>-82.2312</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C10" s="35" t="n">
         <f aca="false">C8+C9</f>
@@ -6919,72 +7324,72 @@
         <v>1994.31425454545</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C11" s="34" t="n">
         <f aca="false">-C10*前提条件!$C$18</f>
-        <v>-731.24856</v>
+        <v>-487.49904</v>
       </c>
       <c r="D11" s="34" t="n">
         <f aca="false">-D10*前提条件!$C$18</f>
-        <v>-1839.20092363636</v>
+        <v>-1226.13394909091</v>
       </c>
       <c r="E11" s="34" t="n">
         <f aca="false">-E10*前提条件!$C$18</f>
-        <v>-897.441414545454</v>
+        <v>-598.294276363636</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="36" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C12" s="37" t="n">
         <f aca="false">C10+C11</f>
-        <v>893.74824</v>
+        <v>1137.49776</v>
       </c>
       <c r="D12" s="37" t="n">
         <f aca="false">D10+D11</f>
-        <v>2247.91224</v>
+        <v>2860.97921454545</v>
       </c>
       <c r="E12" s="37" t="n">
         <f aca="false">E10+E11</f>
-        <v>1096.87284</v>
+        <v>1396.01997818182</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C13" s="38" t="n">
         <f aca="false">C12/C6</f>
-        <v>0.451388</v>
+        <v>0.574493818181818</v>
       </c>
       <c r="D13" s="38" t="n">
         <f aca="false">D12/D6</f>
-        <v>0.451388</v>
+        <v>0.574493818181818</v>
       </c>
       <c r="E13" s="38" t="n">
         <f aca="false">E12/E6</f>
-        <v>0.451388</v>
+        <v>0.574493818181818</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="36" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -6993,135 +7398,135 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="C16" s="39" t="n">
-        <f aca="false">1/前提条件!$C$24</f>
+        <f aca="false">1/前提条件!$C$35</f>
         <v>33.3333333333333</v>
       </c>
       <c r="D16" s="39" t="n">
-        <f aca="false">1/前提条件!$C$24</f>
+        <f aca="false">1/前提条件!$C$35</f>
         <v>33.3333333333333</v>
       </c>
       <c r="E16" s="39" t="n">
-        <f aca="false">1/前提条件!$C$24</f>
+        <f aca="false">1/前提条件!$C$35</f>
         <v>33.3333333333333</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="41" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="C17" s="42" t="n">
         <f aca="false">C12*C16</f>
-        <v>29791.608</v>
+        <v>37916.592</v>
       </c>
       <c r="D17" s="42" t="n">
         <f aca="false">D12*D16</f>
-        <v>74930.408</v>
+        <v>95365.9738181818</v>
       </c>
       <c r="E17" s="42" t="n">
         <f aca="false">E12*E16</f>
-        <v>36562.428</v>
+        <v>46533.9992727273</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="6" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C18" s="32" t="n">
-        <f aca="false">前提条件!$C$27</f>
+        <f aca="false">前提条件!$C$38</f>
         <v>20000</v>
       </c>
       <c r="D18" s="32" t="n">
-        <f aca="false">前提条件!$C$27</f>
+        <f aca="false">前提条件!$C$38</f>
         <v>20000</v>
       </c>
       <c r="E18" s="32" t="n">
-        <f aca="false">前提条件!$C$27</f>
+        <f aca="false">前提条件!$C$38</f>
         <v>20000</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C19" s="43" t="n">
         <f aca="false">C17/C18</f>
-        <v>1.4895804</v>
+        <v>1.8958296</v>
       </c>
       <c r="D19" s="43" t="n">
         <f aca="false">D17/D18</f>
-        <v>3.7465204</v>
+        <v>4.76829869090909</v>
       </c>
       <c r="E19" s="43" t="n">
         <f aca="false">E17/E18</f>
-        <v>1.8281214</v>
+        <v>2.32669996363636</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="41" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="C20" s="44" t="n">
         <f aca="false">C18/C12</f>
-        <v>22.3776664444117</v>
+        <v>17.5824522063235</v>
       </c>
       <c r="D20" s="44" t="n">
         <f aca="false">D18/D12</f>
-        <v>8.89714448994682</v>
+        <v>6.99061352781536</v>
       </c>
       <c r="E20" s="44" t="n">
         <f aca="false">E18/E12</f>
-        <v>18.233654139891</v>
+        <v>14.3264425384858</v>
       </c>
       <c r="F20" s="40" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C22" s="45" t="str">
         <f aca="false">IF(E19&gt;=3,"健全","要改善")</f>
         <v>要改善</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="3" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="12" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="6" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C26" s="46" t="n">
         <v>6000</v>
@@ -7133,7 +7538,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="6" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C27" s="46" t="n">
         <v>10000</v>
@@ -7145,7 +7550,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="6" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C28" s="46" t="n">
         <v>20000</v>
@@ -7157,7 +7562,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="6" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C29" s="46" t="n">
         <v>30000</v>
@@ -7169,7 +7574,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="6" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="C30" s="46" t="n">
         <v>40000</v>
@@ -7181,7 +7586,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C31" s="46" t="n">
         <v>50000</v>
@@ -7193,12 +7598,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="17" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="17" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -7217,7 +7622,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:AL43"/>
+  <dimension ref="B2:AL44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -7227,17 +7632,17 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="47" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C5" s="48" t="n">
         <v>1</v>
@@ -7350,7 +7755,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="36" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -7391,7 +7796,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C7" s="49" t="n">
         <v>0</v>
@@ -7539,305 +7944,305 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^0,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^0,0))</f>
         <v>5</v>
       </c>
       <c r="D8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^1,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^1,0))</f>
         <v>6</v>
       </c>
       <c r="E8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^2,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^2,0))</f>
         <v>7</v>
       </c>
       <c r="F8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^3,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^3,0))</f>
         <v>8</v>
       </c>
       <c r="G8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^4,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^4,0))</f>
         <v>9</v>
       </c>
       <c r="H8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^5,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^5,0))</f>
         <v>10</v>
       </c>
       <c r="I8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^6,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^6,0))</f>
         <v>12</v>
       </c>
       <c r="J8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^7,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^7,0))</f>
         <v>13</v>
       </c>
       <c r="K8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^8,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^8,0))</f>
         <v>15</v>
       </c>
       <c r="L8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^9,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^9,0))</f>
         <v>18</v>
       </c>
       <c r="M8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^10,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^10,0))</f>
         <v>20</v>
       </c>
       <c r="N8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^11,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^11,0))</f>
         <v>23</v>
       </c>
       <c r="O8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^12,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^12,0))</f>
         <v>27</v>
       </c>
       <c r="P8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^13,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^13,0))</f>
         <v>31</v>
       </c>
       <c r="Q8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^14,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^14,0))</f>
         <v>35</v>
       </c>
       <c r="R8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^15,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^15,0))</f>
         <v>41</v>
       </c>
       <c r="S8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^16,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^16,0))</f>
         <v>47</v>
       </c>
       <c r="T8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^17,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^17,0))</f>
         <v>54</v>
       </c>
       <c r="U8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^18,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^18,0))</f>
         <v>62</v>
       </c>
       <c r="V8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^19,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^19,0))</f>
         <v>71</v>
       </c>
       <c r="W8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^20,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^20,0))</f>
         <v>82</v>
       </c>
       <c r="X8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^21,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^21,0))</f>
         <v>94</v>
       </c>
       <c r="Y8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^22,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^22,0))</f>
         <v>108</v>
       </c>
       <c r="Z8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^23,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^23,0))</f>
         <v>120</v>
       </c>
       <c r="AA8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^24,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^24,0))</f>
         <v>120</v>
       </c>
       <c r="AB8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^25,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^25,0))</f>
         <v>120</v>
       </c>
       <c r="AC8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^26,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^26,0))</f>
         <v>120</v>
       </c>
       <c r="AD8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^27,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^27,0))</f>
         <v>120</v>
       </c>
       <c r="AE8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^28,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^28,0))</f>
         <v>120</v>
       </c>
       <c r="AF8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^29,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^29,0))</f>
         <v>120</v>
       </c>
       <c r="AG8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^30,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^30,0))</f>
         <v>120</v>
       </c>
       <c r="AH8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^31,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^31,0))</f>
         <v>120</v>
       </c>
       <c r="AI8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^32,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^32,0))</f>
         <v>120</v>
       </c>
       <c r="AJ8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^33,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^33,0))</f>
         <v>120</v>
       </c>
       <c r="AK8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^34,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^34,0))</f>
         <v>120</v>
       </c>
       <c r="AL8" s="49" t="n">
-        <f aca="false">MIN(前提条件!$C$23,ROUND(前提条件!$C$21*(1+前提条件!$C$22)^35,0))</f>
+        <f aca="false">MIN(前提条件!$C$34,ROUND(前提条件!$C$32*(1+前提条件!$C$33)^35,0))</f>
         <v>120</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="C9" s="49" t="n">
-        <f aca="false">-ROUND(C7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(C7*前提条件!$C$35,0)</f>
         <v>-0</v>
       </c>
       <c r="D9" s="49" t="n">
-        <f aca="false">-ROUND(D7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(D7*前提条件!$C$35,0)</f>
         <v>-0</v>
       </c>
       <c r="E9" s="49" t="n">
-        <f aca="false">-ROUND(E7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(E7*前提条件!$C$35,0)</f>
         <v>-0</v>
       </c>
       <c r="F9" s="49" t="n">
-        <f aca="false">-ROUND(F7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(F7*前提条件!$C$35,0)</f>
         <v>-1</v>
       </c>
       <c r="G9" s="49" t="n">
-        <f aca="false">-ROUND(G7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(G7*前提条件!$C$35,0)</f>
         <v>-1</v>
       </c>
       <c r="H9" s="49" t="n">
-        <f aca="false">-ROUND(H7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(H7*前提条件!$C$35,0)</f>
         <v>-1</v>
       </c>
       <c r="I9" s="49" t="n">
-        <f aca="false">-ROUND(I7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(I7*前提条件!$C$35,0)</f>
         <v>-1</v>
       </c>
       <c r="J9" s="49" t="n">
-        <f aca="false">-ROUND(J7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(J7*前提条件!$C$35,0)</f>
         <v>-2</v>
       </c>
       <c r="K9" s="49" t="n">
-        <f aca="false">-ROUND(K7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(K7*前提条件!$C$35,0)</f>
         <v>-2</v>
       </c>
       <c r="L9" s="49" t="n">
-        <f aca="false">-ROUND(L7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(L7*前提条件!$C$35,0)</f>
         <v>-2</v>
       </c>
       <c r="M9" s="49" t="n">
-        <f aca="false">-ROUND(M7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(M7*前提条件!$C$35,0)</f>
         <v>-3</v>
       </c>
       <c r="N9" s="49" t="n">
-        <f aca="false">-ROUND(N7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(N7*前提条件!$C$35,0)</f>
         <v>-3</v>
       </c>
       <c r="O9" s="49" t="n">
-        <f aca="false">-ROUND(O7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(O7*前提条件!$C$35,0)</f>
         <v>-4</v>
       </c>
       <c r="P9" s="49" t="n">
-        <f aca="false">-ROUND(P7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(P7*前提条件!$C$35,0)</f>
         <v>-5</v>
       </c>
       <c r="Q9" s="49" t="n">
-        <f aca="false">-ROUND(Q7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(Q7*前提条件!$C$35,0)</f>
         <v>-5</v>
       </c>
       <c r="R9" s="49" t="n">
-        <f aca="false">-ROUND(R7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(R7*前提条件!$C$35,0)</f>
         <v>-6</v>
       </c>
       <c r="S9" s="49" t="n">
-        <f aca="false">-ROUND(S7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(S7*前提条件!$C$35,0)</f>
         <v>-7</v>
       </c>
       <c r="T9" s="49" t="n">
-        <f aca="false">-ROUND(T7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(T7*前提条件!$C$35,0)</f>
         <v>-9</v>
       </c>
       <c r="U9" s="49" t="n">
-        <f aca="false">-ROUND(U7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(U7*前提条件!$C$35,0)</f>
         <v>-10</v>
       </c>
       <c r="V9" s="49" t="n">
-        <f aca="false">-ROUND(V7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(V7*前提条件!$C$35,0)</f>
         <v>-11</v>
       </c>
       <c r="W9" s="49" t="n">
-        <f aca="false">-ROUND(W7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(W7*前提条件!$C$35,0)</f>
         <v>-13</v>
       </c>
       <c r="X9" s="49" t="n">
-        <f aca="false">-ROUND(X7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(X7*前提条件!$C$35,0)</f>
         <v>-15</v>
       </c>
       <c r="Y9" s="49" t="n">
-        <f aca="false">-ROUND(Y7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(Y7*前提条件!$C$35,0)</f>
         <v>-18</v>
       </c>
       <c r="Z9" s="49" t="n">
-        <f aca="false">-ROUND(Z7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(Z7*前提条件!$C$35,0)</f>
         <v>-20</v>
       </c>
       <c r="AA9" s="49" t="n">
-        <f aca="false">-ROUND(AA7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AA7*前提条件!$C$35,0)</f>
         <v>-23</v>
       </c>
       <c r="AB9" s="49" t="n">
-        <f aca="false">-ROUND(AB7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AB7*前提条件!$C$35,0)</f>
         <v>-26</v>
       </c>
       <c r="AC9" s="49" t="n">
-        <f aca="false">-ROUND(AC7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AC7*前提条件!$C$35,0)</f>
         <v>-29</v>
       </c>
       <c r="AD9" s="49" t="n">
-        <f aca="false">-ROUND(AD7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AD7*前提条件!$C$35,0)</f>
         <v>-32</v>
       </c>
       <c r="AE9" s="49" t="n">
-        <f aca="false">-ROUND(AE7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AE7*前提条件!$C$35,0)</f>
         <v>-34</v>
       </c>
       <c r="AF9" s="49" t="n">
-        <f aca="false">-ROUND(AF7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AF7*前提条件!$C$35,0)</f>
         <v>-37</v>
       </c>
       <c r="AG9" s="49" t="n">
-        <f aca="false">-ROUND(AG7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AG7*前提条件!$C$35,0)</f>
         <v>-40</v>
       </c>
       <c r="AH9" s="49" t="n">
-        <f aca="false">-ROUND(AH7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AH7*前提条件!$C$35,0)</f>
         <v>-42</v>
       </c>
       <c r="AI9" s="49" t="n">
-        <f aca="false">-ROUND(AI7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AI7*前提条件!$C$35,0)</f>
         <v>-44</v>
       </c>
       <c r="AJ9" s="49" t="n">
-        <f aca="false">-ROUND(AJ7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AJ7*前提条件!$C$35,0)</f>
         <v>-47</v>
       </c>
       <c r="AK9" s="49" t="n">
-        <f aca="false">-ROUND(AK7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AK7*前提条件!$C$35,0)</f>
         <v>-49</v>
       </c>
       <c r="AL9" s="49" t="n">
-        <f aca="false">-ROUND(AL7*前提条件!$C$24,0)</f>
+        <f aca="false">-ROUND(AL7*前提条件!$C$35,0)</f>
         <v>-51</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C10" s="50" t="n">
         <f aca="false">C7+C8+C9</f>
@@ -7986,7 +8391,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="C11" s="51" t="n">
         <f aca="false">(C7+C10)/2</f>
@@ -8135,7 +8540,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="36" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -8176,7 +8581,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C14" s="52" t="n">
         <f aca="false">C11*単位経済!$E$7</f>
@@ -8325,7 +8730,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C15" s="52" t="n">
         <f aca="false">-C14*前提条件!$C$16/(1+前提条件!$C$16)</f>
@@ -8474,7 +8879,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C16" s="52" t="n">
         <f aca="false">-C14*前提条件!$C$17</f>
@@ -8623,7 +9028,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C17" s="53" t="n">
         <f aca="false">C14+C15+C16</f>
@@ -8772,2044 +9177,2193 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18" s="52" t="n">
-        <f aca="false">-C17*前提条件!$C$18</f>
-        <v>-2243.60353636364</v>
-      </c>
-      <c r="D18" s="52" t="n">
-        <f aca="false">-D17*前提条件!$C$18</f>
-        <v>-7179.53131636364</v>
-      </c>
-      <c r="E18" s="52" t="n">
-        <f aca="false">-E17*前提条件!$C$18</f>
-        <v>-13012.9005109091</v>
-      </c>
-      <c r="F18" s="52" t="n">
-        <f aca="false">-F17*前提条件!$C$18</f>
-        <v>-19294.9904127273</v>
-      </c>
-      <c r="G18" s="52" t="n">
-        <f aca="false">-G17*前提条件!$C$18</f>
-        <v>-26025.8010218182</v>
-      </c>
-      <c r="H18" s="52" t="n">
-        <f aca="false">-H17*前提条件!$C$18</f>
-        <v>-33654.0530454545</v>
-      </c>
-      <c r="I18" s="52" t="n">
-        <f aca="false">-I17*前提条件!$C$18</f>
-        <v>-42628.4671909091</v>
-      </c>
-      <c r="J18" s="52" t="n">
-        <f aca="false">-J17*前提条件!$C$18</f>
-        <v>-52500.3227509091</v>
-      </c>
-      <c r="K18" s="52" t="n">
-        <f aca="false">-K17*前提条件!$C$18</f>
-        <v>-63269.6197254545</v>
-      </c>
-      <c r="L18" s="52" t="n">
-        <f aca="false">-L17*前提条件!$C$18</f>
-        <v>-76282.5202363636</v>
-      </c>
-      <c r="M18" s="52" t="n">
-        <f aca="false">-M17*前提条件!$C$18</f>
-        <v>-91090.3035763636</v>
-      </c>
-      <c r="N18" s="52" t="n">
-        <f aca="false">-N17*前提条件!$C$18</f>
-        <v>-107692.969745455</v>
-      </c>
-      <c r="O18" s="52" t="n">
-        <f aca="false">-O17*前提条件!$C$18</f>
-        <v>-126987.960158182</v>
-      </c>
-      <c r="P18" s="52" t="n">
-        <f aca="false">-P17*前提条件!$C$18</f>
-        <v>-148975.274814545</v>
-      </c>
-      <c r="Q18" s="52" t="n">
-        <f aca="false">-Q17*前提条件!$C$18</f>
-        <v>-174103.634421818</v>
-      </c>
-      <c r="R18" s="52" t="n">
-        <f aca="false">-R17*前提条件!$C$18</f>
-        <v>-203270.480394545</v>
-      </c>
-      <c r="S18" s="52" t="n">
-        <f aca="false">-S17*前提条件!$C$18</f>
-        <v>-236924.53344</v>
-      </c>
-      <c r="T18" s="52" t="n">
-        <f aca="false">-T17*前提条件!$C$18</f>
-        <v>-275065.793558182</v>
-      </c>
-      <c r="U18" s="52" t="n">
-        <f aca="false">-U17*前提条件!$C$18</f>
-        <v>-318591.702163636</v>
-      </c>
-      <c r="V18" s="52" t="n">
-        <f aca="false">-V17*前提条件!$C$18</f>
-        <v>-368848.421378182</v>
-      </c>
-      <c r="W18" s="52" t="n">
-        <f aca="false">-W17*前提条件!$C$18</f>
-        <v>-426733.392616364</v>
-      </c>
-      <c r="X18" s="52" t="n">
-        <f aca="false">-X17*前提条件!$C$18</f>
-        <v>-493144.057292727</v>
-      </c>
-      <c r="Y18" s="52" t="n">
-        <f aca="false">-Y17*前提条件!$C$18</f>
-        <v>-568977.856821818</v>
-      </c>
-      <c r="Z18" s="52" t="n">
-        <f aca="false">-Z17*前提条件!$C$18</f>
-        <v>-654234.791203636</v>
-      </c>
-      <c r="AA18" s="52" t="n">
-        <f aca="false">-AA17*前提条件!$C$18</f>
-        <v>-742632.770536364</v>
-      </c>
-      <c r="AB18" s="52" t="n">
-        <f aca="false">-AB17*前提条件!$C$18</f>
-        <v>-828338.425625454</v>
-      </c>
-      <c r="AC18" s="52" t="n">
-        <f aca="false">-AC17*前提条件!$C$18</f>
-        <v>-911351.756470909</v>
-      </c>
-      <c r="AD18" s="52" t="n">
-        <f aca="false">-AD17*前提条件!$C$18</f>
-        <v>-991672.763072728</v>
-      </c>
-      <c r="AE18" s="52" t="n">
-        <f aca="false">-AE17*前提条件!$C$18</f>
-        <v>-1069750.16613818</v>
-      </c>
-      <c r="AF18" s="52" t="n">
-        <f aca="false">-AF17*前提条件!$C$18</f>
-        <v>-1145583.96566727</v>
-      </c>
-      <c r="AG18" s="52" t="n">
-        <f aca="false">-AG17*前提条件!$C$18</f>
-        <v>-1218725.44095273</v>
-      </c>
-      <c r="AH18" s="52" t="n">
-        <f aca="false">-AH17*前提条件!$C$18</f>
-        <v>-1289623.31270182</v>
-      </c>
-      <c r="AI18" s="52" t="n">
-        <f aca="false">-AI17*前提条件!$C$18</f>
-        <v>-1358726.30162182</v>
-      </c>
-      <c r="AJ18" s="52" t="n">
-        <f aca="false">-AJ17*前提条件!$C$18</f>
-        <v>-1425585.68700545</v>
-      </c>
-      <c r="AK18" s="52" t="n">
-        <f aca="false">-AK17*前提条件!$C$18</f>
-        <v>-1490201.46885273</v>
-      </c>
-      <c r="AL18" s="52" t="n">
-        <f aca="false">-AL17*前提条件!$C$18</f>
-        <v>-1553022.36787091</v>
+        <v>183</v>
+      </c>
+      <c r="C18" s="54" t="n">
+        <f aca="false">IF(C10&lt;=前提条件!$C$21,前提条件!$C$22,IF(C10&lt;=前提条件!$C$23,前提条件!$C$24,IF(C10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27)))</f>
+        <v>0.3</v>
+      </c>
+      <c r="D18" s="54" t="n">
+        <f aca="false">MAX(C18,IF(D10&lt;=前提条件!$C$21,前提条件!$C$22,IF(D10&lt;=前提条件!$C$23,前提条件!$C$24,IF(D10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="54" t="n">
+        <f aca="false">MAX(D18,IF(E10&lt;=前提条件!$C$21,前提条件!$C$22,IF(E10&lt;=前提条件!$C$23,前提条件!$C$24,IF(E10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="F18" s="54" t="n">
+        <f aca="false">MAX(E18,IF(F10&lt;=前提条件!$C$21,前提条件!$C$22,IF(F10&lt;=前提条件!$C$23,前提条件!$C$24,IF(F10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="G18" s="54" t="n">
+        <f aca="false">MAX(F18,IF(G10&lt;=前提条件!$C$21,前提条件!$C$22,IF(G10&lt;=前提条件!$C$23,前提条件!$C$24,IF(G10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="H18" s="54" t="n">
+        <f aca="false">MAX(G18,IF(H10&lt;=前提条件!$C$21,前提条件!$C$22,IF(H10&lt;=前提条件!$C$23,前提条件!$C$24,IF(H10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="I18" s="54" t="n">
+        <f aca="false">MAX(H18,IF(I10&lt;=前提条件!$C$21,前提条件!$C$22,IF(I10&lt;=前提条件!$C$23,前提条件!$C$24,IF(I10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="J18" s="54" t="n">
+        <f aca="false">MAX(I18,IF(J10&lt;=前提条件!$C$21,前提条件!$C$22,IF(J10&lt;=前提条件!$C$23,前提条件!$C$24,IF(J10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="K18" s="54" t="n">
+        <f aca="false">MAX(J18,IF(K10&lt;=前提条件!$C$21,前提条件!$C$22,IF(K10&lt;=前提条件!$C$23,前提条件!$C$24,IF(K10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="L18" s="54" t="n">
+        <f aca="false">MAX(K18,IF(L10&lt;=前提条件!$C$21,前提条件!$C$22,IF(L10&lt;=前提条件!$C$23,前提条件!$C$24,IF(L10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="M18" s="54" t="n">
+        <f aca="false">MAX(L18,IF(M10&lt;=前提条件!$C$21,前提条件!$C$22,IF(M10&lt;=前提条件!$C$23,前提条件!$C$24,IF(M10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="N18" s="54" t="n">
+        <f aca="false">MAX(M18,IF(N10&lt;=前提条件!$C$21,前提条件!$C$22,IF(N10&lt;=前提条件!$C$23,前提条件!$C$24,IF(N10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="O18" s="54" t="n">
+        <f aca="false">MAX(N18,IF(O10&lt;=前提条件!$C$21,前提条件!$C$22,IF(O10&lt;=前提条件!$C$23,前提条件!$C$24,IF(O10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="P18" s="54" t="n">
+        <f aca="false">MAX(O18,IF(P10&lt;=前提条件!$C$21,前提条件!$C$22,IF(P10&lt;=前提条件!$C$23,前提条件!$C$24,IF(P10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="Q18" s="54" t="n">
+        <f aca="false">MAX(P18,IF(Q10&lt;=前提条件!$C$21,前提条件!$C$22,IF(Q10&lt;=前提条件!$C$23,前提条件!$C$24,IF(Q10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="R18" s="54" t="n">
+        <f aca="false">MAX(Q18,IF(R10&lt;=前提条件!$C$21,前提条件!$C$22,IF(R10&lt;=前提条件!$C$23,前提条件!$C$24,IF(R10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="S18" s="54" t="n">
+        <f aca="false">MAX(R18,IF(S10&lt;=前提条件!$C$21,前提条件!$C$22,IF(S10&lt;=前提条件!$C$23,前提条件!$C$24,IF(S10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="T18" s="54" t="n">
+        <f aca="false">MAX(S18,IF(T10&lt;=前提条件!$C$21,前提条件!$C$22,IF(T10&lt;=前提条件!$C$23,前提条件!$C$24,IF(T10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="U18" s="54" t="n">
+        <f aca="false">MAX(T18,IF(U10&lt;=前提条件!$C$21,前提条件!$C$22,IF(U10&lt;=前提条件!$C$23,前提条件!$C$24,IF(U10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="V18" s="54" t="n">
+        <f aca="false">MAX(U18,IF(V10&lt;=前提条件!$C$21,前提条件!$C$22,IF(V10&lt;=前提条件!$C$23,前提条件!$C$24,IF(V10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.3</v>
+      </c>
+      <c r="W18" s="54" t="n">
+        <f aca="false">MAX(V18,IF(W10&lt;=前提条件!$C$21,前提条件!$C$22,IF(W10&lt;=前提条件!$C$23,前提条件!$C$24,IF(W10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="X18" s="54" t="n">
+        <f aca="false">MAX(W18,IF(X10&lt;=前提条件!$C$21,前提条件!$C$22,IF(X10&lt;=前提条件!$C$23,前提条件!$C$24,IF(X10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="Y18" s="54" t="n">
+        <f aca="false">MAX(X18,IF(Y10&lt;=前提条件!$C$21,前提条件!$C$22,IF(Y10&lt;=前提条件!$C$23,前提条件!$C$24,IF(Y10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="Z18" s="54" t="n">
+        <f aca="false">MAX(Y18,IF(Z10&lt;=前提条件!$C$21,前提条件!$C$22,IF(Z10&lt;=前提条件!$C$23,前提条件!$C$24,IF(Z10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="AA18" s="54" t="n">
+        <f aca="false">MAX(Z18,IF(AA10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AA10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AA10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="AB18" s="54" t="n">
+        <f aca="false">MAX(AA18,IF(AB10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AB10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AB10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="AC18" s="54" t="n">
+        <f aca="false">MAX(AB18,IF(AC10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AC10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AC10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="AD18" s="54" t="n">
+        <f aca="false">MAX(AC18,IF(AD10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AD10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AD10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="AE18" s="54" t="n">
+        <f aca="false">MAX(AD18,IF(AE10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AE10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AE10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="AF18" s="54" t="n">
+        <f aca="false">MAX(AE18,IF(AF10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AF10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AF10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="AG18" s="54" t="n">
+        <f aca="false">MAX(AF18,IF(AG10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AG10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AG10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="AH18" s="54" t="n">
+        <f aca="false">MAX(AG18,IF(AH10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AH10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AH10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.35</v>
+      </c>
+      <c r="AI18" s="54" t="n">
+        <f aca="false">MAX(AH18,IF(AI10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AI10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AI10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.4</v>
+      </c>
+      <c r="AJ18" s="54" t="n">
+        <f aca="false">MAX(AI18,IF(AJ10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AJ10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AJ10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.4</v>
+      </c>
+      <c r="AK18" s="54" t="n">
+        <f aca="false">MAX(AJ18,IF(AK10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AK10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AK10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.4</v>
+      </c>
+      <c r="AL18" s="54" t="n">
+        <f aca="false">MAX(AK18,IF(AL10&lt;=前提条件!$C$21,前提条件!$C$22,IF(AL10&lt;=前提条件!$C$23,前提条件!$C$24,IF(AL10&lt;=前提条件!$C$25,前提条件!$C$26,前提条件!$C$27))))</f>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="36" t="s">
-        <v>172</v>
-      </c>
-      <c r="C19" s="54" t="n">
-        <f aca="false">C17+C18</f>
-        <v>2742.1821</v>
-      </c>
-      <c r="D19" s="54" t="n">
-        <f aca="false">D17+D18</f>
-        <v>8774.98272</v>
-      </c>
-      <c r="E19" s="54" t="n">
-        <f aca="false">E17+E18</f>
-        <v>15904.65618</v>
-      </c>
-      <c r="F19" s="54" t="n">
-        <f aca="false">F17+F18</f>
-        <v>23582.76606</v>
-      </c>
-      <c r="G19" s="54" t="n">
-        <f aca="false">G17+G18</f>
-        <v>31809.31236</v>
-      </c>
-      <c r="H19" s="54" t="n">
-        <f aca="false">H17+H18</f>
-        <v>41132.7315</v>
-      </c>
-      <c r="I19" s="54" t="n">
-        <f aca="false">I17+I18</f>
-        <v>52101.4599</v>
-      </c>
-      <c r="J19" s="54" t="n">
-        <f aca="false">J17+J18</f>
-        <v>64167.06114</v>
-      </c>
-      <c r="K19" s="54" t="n">
-        <f aca="false">K17+K18</f>
-        <v>77329.53522</v>
-      </c>
-      <c r="L19" s="54" t="n">
-        <f aca="false">L17+L18</f>
-        <v>93234.1914</v>
-      </c>
-      <c r="M19" s="54" t="n">
-        <f aca="false">M17+M18</f>
-        <v>111332.59326</v>
-      </c>
-      <c r="N19" s="54" t="n">
-        <f aca="false">N17+N18</f>
-        <v>131624.7408</v>
-      </c>
-      <c r="O19" s="54" t="n">
-        <f aca="false">O17+O18</f>
-        <v>155207.50686</v>
-      </c>
-      <c r="P19" s="54" t="n">
-        <f aca="false">P17+P18</f>
-        <v>182080.89144</v>
-      </c>
-      <c r="Q19" s="54" t="n">
-        <f aca="false">Q17+Q18</f>
-        <v>212793.33096</v>
-      </c>
-      <c r="R19" s="54" t="n">
-        <f aca="false">R17+R18</f>
-        <v>248441.69826</v>
-      </c>
-      <c r="S19" s="54" t="n">
-        <f aca="false">S17+S18</f>
-        <v>289574.42976</v>
-      </c>
-      <c r="T19" s="54" t="n">
-        <f aca="false">T17+T18</f>
-        <v>336191.52546</v>
-      </c>
-      <c r="U19" s="54" t="n">
-        <f aca="false">U17+U18</f>
-        <v>389389.8582</v>
-      </c>
-      <c r="V19" s="54" t="n">
-        <f aca="false">V17+V18</f>
-        <v>450814.73724</v>
-      </c>
-      <c r="W19" s="54" t="n">
-        <f aca="false">W17+W18</f>
-        <v>521563.03542</v>
-      </c>
-      <c r="X19" s="54" t="n">
-        <f aca="false">X17+X18</f>
-        <v>602731.62558</v>
-      </c>
-      <c r="Y19" s="54" t="n">
-        <f aca="false">Y17+Y18</f>
-        <v>695417.38056</v>
-      </c>
-      <c r="Z19" s="54" t="n">
-        <f aca="false">Z17+Z18</f>
-        <v>799620.30036</v>
-      </c>
-      <c r="AA19" s="54" t="n">
-        <f aca="false">AA17+AA18</f>
-        <v>907662.2751</v>
-      </c>
-      <c r="AB19" s="54" t="n">
-        <f aca="false">AB17+AB18</f>
-        <v>1012413.63132</v>
-      </c>
-      <c r="AC19" s="54" t="n">
-        <f aca="false">AC17+AC18</f>
-        <v>1113874.36902</v>
-      </c>
-      <c r="AD19" s="54" t="n">
-        <f aca="false">AD17+AD18</f>
-        <v>1212044.4882</v>
-      </c>
-      <c r="AE19" s="54" t="n">
-        <f aca="false">AE17+AE18</f>
-        <v>1307472.42528</v>
-      </c>
-      <c r="AF19" s="54" t="n">
-        <f aca="false">AF17+AF18</f>
-        <v>1400158.18026</v>
-      </c>
-      <c r="AG19" s="54" t="n">
-        <f aca="false">AG17+AG18</f>
-        <v>1489553.31672</v>
-      </c>
-      <c r="AH19" s="54" t="n">
-        <f aca="false">AH17+AH18</f>
-        <v>1576206.27108</v>
-      </c>
-      <c r="AI19" s="54" t="n">
-        <f aca="false">AI17+AI18</f>
-        <v>1660665.47976</v>
-      </c>
-      <c r="AJ19" s="54" t="n">
-        <f aca="false">AJ17+AJ18</f>
-        <v>1742382.50634</v>
-      </c>
-      <c r="AK19" s="54" t="n">
-        <f aca="false">AK17+AK18</f>
-        <v>1821357.35082</v>
-      </c>
-      <c r="AL19" s="54" t="n">
-        <f aca="false">AL17+AL18</f>
-        <v>1898138.44962</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
-      <c r="AF21" s="14"/>
-      <c r="AG21" s="14"/>
-      <c r="AH21" s="14"/>
-      <c r="AI21" s="14"/>
-      <c r="AJ21" s="14"/>
-      <c r="AK21" s="14"/>
-      <c r="AL21" s="14"/>
+      <c r="B19" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="52" t="n">
+        <f aca="false">-C17*C18</f>
+        <v>-1495.73569090909</v>
+      </c>
+      <c r="D19" s="52" t="n">
+        <f aca="false">-D17*D18</f>
+        <v>-4786.35421090909</v>
+      </c>
+      <c r="E19" s="52" t="n">
+        <f aca="false">-E17*E18</f>
+        <v>-8675.26700727273</v>
+      </c>
+      <c r="F19" s="52" t="n">
+        <f aca="false">-F17*F18</f>
+        <v>-12863.3269418182</v>
+      </c>
+      <c r="G19" s="52" t="n">
+        <f aca="false">-G17*G18</f>
+        <v>-17350.5340145455</v>
+      </c>
+      <c r="H19" s="52" t="n">
+        <f aca="false">-H17*H18</f>
+        <v>-22436.0353636364</v>
+      </c>
+      <c r="I19" s="52" t="n">
+        <f aca="false">-I17*I18</f>
+        <v>-28418.9781272727</v>
+      </c>
+      <c r="J19" s="52" t="n">
+        <f aca="false">-J17*J18</f>
+        <v>-35000.2151672727</v>
+      </c>
+      <c r="K19" s="52" t="n">
+        <f aca="false">-K17*K18</f>
+        <v>-42179.7464836364</v>
+      </c>
+      <c r="L19" s="52" t="n">
+        <f aca="false">-L17*L18</f>
+        <v>-50855.0134909091</v>
+      </c>
+      <c r="M19" s="52" t="n">
+        <f aca="false">-M17*M18</f>
+        <v>-60726.8690509091</v>
+      </c>
+      <c r="N19" s="52" t="n">
+        <f aca="false">-N17*N18</f>
+        <v>-71795.3131636364</v>
+      </c>
+      <c r="O19" s="52" t="n">
+        <f aca="false">-O17*O18</f>
+        <v>-84658.6401054545</v>
+      </c>
+      <c r="P19" s="52" t="n">
+        <f aca="false">-P17*P18</f>
+        <v>-99316.8498763636</v>
+      </c>
+      <c r="Q19" s="52" t="n">
+        <f aca="false">-Q17*Q18</f>
+        <v>-116069.089614545</v>
+      </c>
+      <c r="R19" s="52" t="n">
+        <f aca="false">-R17*R18</f>
+        <v>-135513.653596364</v>
+      </c>
+      <c r="S19" s="52" t="n">
+        <f aca="false">-S17*S18</f>
+        <v>-157949.68896</v>
+      </c>
+      <c r="T19" s="52" t="n">
+        <f aca="false">-T17*T18</f>
+        <v>-183377.195705455</v>
+      </c>
+      <c r="U19" s="52" t="n">
+        <f aca="false">-U17*U18</f>
+        <v>-212394.468109091</v>
+      </c>
+      <c r="V19" s="52" t="n">
+        <f aca="false">-V17*V18</f>
+        <v>-245898.947585455</v>
+      </c>
+      <c r="W19" s="52" t="n">
+        <f aca="false">-W17*W18</f>
+        <v>-331903.749812727</v>
+      </c>
+      <c r="X19" s="52" t="n">
+        <f aca="false">-X17*X18</f>
+        <v>-383556.489005455</v>
+      </c>
+      <c r="Y19" s="52" t="n">
+        <f aca="false">-Y17*Y18</f>
+        <v>-442538.333083636</v>
+      </c>
+      <c r="Z19" s="52" t="n">
+        <f aca="false">-Z17*Z18</f>
+        <v>-508849.282047273</v>
+      </c>
+      <c r="AA19" s="52" t="n">
+        <f aca="false">-AA17*AA18</f>
+        <v>-577603.265972727</v>
+      </c>
+      <c r="AB19" s="52" t="n">
+        <f aca="false">-AB17*AB18</f>
+        <v>-644263.219930909</v>
+      </c>
+      <c r="AC19" s="52" t="n">
+        <f aca="false">-AC17*AC18</f>
+        <v>-708829.143921818</v>
+      </c>
+      <c r="AD19" s="52" t="n">
+        <f aca="false">-AD17*AD18</f>
+        <v>-771301.037945455</v>
+      </c>
+      <c r="AE19" s="52" t="n">
+        <f aca="false">-AE17*AE18</f>
+        <v>-832027.906996364</v>
+      </c>
+      <c r="AF19" s="52" t="n">
+        <f aca="false">-AF17*AF18</f>
+        <v>-891009.751074545</v>
+      </c>
+      <c r="AG19" s="52" t="n">
+        <f aca="false">-AG17*AG18</f>
+        <v>-947897.565185454</v>
+      </c>
+      <c r="AH19" s="52" t="n">
+        <f aca="false">-AH17*AH18</f>
+        <v>-1003040.35432364</v>
+      </c>
+      <c r="AI19" s="52" t="n">
+        <f aca="false">-AI17*AI18</f>
+        <v>-1207756.71255273</v>
+      </c>
+      <c r="AJ19" s="52" t="n">
+        <f aca="false">-AJ17*AJ18</f>
+        <v>-1267187.27733818</v>
+      </c>
+      <c r="AK19" s="52" t="n">
+        <f aca="false">-AK17*AK18</f>
+        <v>-1324623.52786909</v>
+      </c>
+      <c r="AL19" s="52" t="n">
+        <f aca="false">-AL17*AL18</f>
+        <v>-1380464.32699636</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" s="55" t="n">
+        <f aca="false">C17+C19</f>
+        <v>3490.04994545455</v>
+      </c>
+      <c r="D20" s="55" t="n">
+        <f aca="false">D17+D19</f>
+        <v>11168.1598254545</v>
+      </c>
+      <c r="E20" s="55" t="n">
+        <f aca="false">E17+E19</f>
+        <v>20242.2896836364</v>
+      </c>
+      <c r="F20" s="55" t="n">
+        <f aca="false">F17+F19</f>
+        <v>30014.4295309091</v>
+      </c>
+      <c r="G20" s="55" t="n">
+        <f aca="false">G17+G19</f>
+        <v>40484.5793672727</v>
+      </c>
+      <c r="H20" s="55" t="n">
+        <f aca="false">H17+H19</f>
+        <v>52350.7491818182</v>
+      </c>
+      <c r="I20" s="55" t="n">
+        <f aca="false">I17+I19</f>
+        <v>66310.9489636364</v>
+      </c>
+      <c r="J20" s="55" t="n">
+        <f aca="false">J17+J19</f>
+        <v>81667.1687236364</v>
+      </c>
+      <c r="K20" s="55" t="n">
+        <f aca="false">K17+K19</f>
+        <v>98419.4084618182</v>
+      </c>
+      <c r="L20" s="55" t="n">
+        <f aca="false">L17+L19</f>
+        <v>118661.698145455</v>
+      </c>
+      <c r="M20" s="55" t="n">
+        <f aca="false">M17+M19</f>
+        <v>141696.027785455</v>
+      </c>
+      <c r="N20" s="55" t="n">
+        <f aca="false">N17+N19</f>
+        <v>167522.397381818</v>
+      </c>
+      <c r="O20" s="55" t="n">
+        <f aca="false">O17+O19</f>
+        <v>197536.826912727</v>
+      </c>
+      <c r="P20" s="55" t="n">
+        <f aca="false">P17+P19</f>
+        <v>231739.316378182</v>
+      </c>
+      <c r="Q20" s="55" t="n">
+        <f aca="false">Q17+Q19</f>
+        <v>270827.875767273</v>
+      </c>
+      <c r="R20" s="55" t="n">
+        <f aca="false">R17+R19</f>
+        <v>316198.525058182</v>
+      </c>
+      <c r="S20" s="55" t="n">
+        <f aca="false">S17+S19</f>
+        <v>368549.27424</v>
+      </c>
+      <c r="T20" s="55" t="n">
+        <f aca="false">T17+T19</f>
+        <v>427880.123312727</v>
+      </c>
+      <c r="U20" s="55" t="n">
+        <f aca="false">U17+U19</f>
+        <v>495587.092254545</v>
+      </c>
+      <c r="V20" s="55" t="n">
+        <f aca="false">V17+V19</f>
+        <v>573764.211032727</v>
+      </c>
+      <c r="W20" s="55" t="n">
+        <f aca="false">W17+W19</f>
+        <v>616392.678223636</v>
+      </c>
+      <c r="X20" s="55" t="n">
+        <f aca="false">X17+X19</f>
+        <v>712319.193867273</v>
+      </c>
+      <c r="Y20" s="55" t="n">
+        <f aca="false">Y17+Y19</f>
+        <v>821856.904298182</v>
+      </c>
+      <c r="Z20" s="55" t="n">
+        <f aca="false">Z17+Z19</f>
+        <v>945005.809516364</v>
+      </c>
+      <c r="AA20" s="55" t="n">
+        <f aca="false">AA17+AA19</f>
+        <v>1072691.77966364</v>
+      </c>
+      <c r="AB20" s="55" t="n">
+        <f aca="false">AB17+AB19</f>
+        <v>1196488.83701455</v>
+      </c>
+      <c r="AC20" s="55" t="n">
+        <f aca="false">AC17+AC19</f>
+        <v>1316396.98156909</v>
+      </c>
+      <c r="AD20" s="55" t="n">
+        <f aca="false">AD17+AD19</f>
+        <v>1432416.21332727</v>
+      </c>
+      <c r="AE20" s="55" t="n">
+        <f aca="false">AE17+AE19</f>
+        <v>1545194.68442182</v>
+      </c>
+      <c r="AF20" s="55" t="n">
+        <f aca="false">AF17+AF19</f>
+        <v>1654732.39485273</v>
+      </c>
+      <c r="AG20" s="55" t="n">
+        <f aca="false">AG17+AG19</f>
+        <v>1760381.19248727</v>
+      </c>
+      <c r="AH20" s="55" t="n">
+        <f aca="false">AH17+AH19</f>
+        <v>1862789.22945818</v>
+      </c>
+      <c r="AI20" s="55" t="n">
+        <f aca="false">AI17+AI19</f>
+        <v>1811635.06882909</v>
+      </c>
+      <c r="AJ20" s="55" t="n">
+        <f aca="false">AJ17+AJ19</f>
+        <v>1900780.91600727</v>
+      </c>
+      <c r="AK20" s="55" t="n">
+        <f aca="false">AK17+AK19</f>
+        <v>1986935.29180364</v>
+      </c>
+      <c r="AL20" s="55" t="n">
+        <f aca="false">AL17+AL19</f>
+        <v>2070696.49049455</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*1</f>
-        <v>5000</v>
-      </c>
-      <c r="D22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*2</f>
-        <v>7000</v>
-      </c>
-      <c r="E22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*3</f>
-        <v>9000</v>
-      </c>
-      <c r="F22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*4</f>
-        <v>11000</v>
-      </c>
-      <c r="G22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*5</f>
-        <v>13000</v>
-      </c>
-      <c r="H22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*6</f>
-        <v>15000</v>
-      </c>
-      <c r="I22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*7</f>
-        <v>17000</v>
-      </c>
-      <c r="J22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*8</f>
-        <v>19000</v>
-      </c>
-      <c r="K22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*9</f>
-        <v>21000</v>
-      </c>
-      <c r="L22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*10</f>
-        <v>23000</v>
-      </c>
-      <c r="M22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*11</f>
-        <v>25000</v>
-      </c>
-      <c r="N22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*12</f>
-        <v>27000</v>
-      </c>
-      <c r="O22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*13</f>
-        <v>29000</v>
-      </c>
-      <c r="P22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*14</f>
-        <v>31000</v>
-      </c>
-      <c r="Q22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*15</f>
-        <v>33000</v>
-      </c>
-      <c r="R22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*16</f>
-        <v>35000</v>
-      </c>
-      <c r="S22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*17</f>
-        <v>37000</v>
-      </c>
-      <c r="T22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*18</f>
-        <v>39000</v>
-      </c>
-      <c r="U22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*19</f>
-        <v>41000</v>
-      </c>
-      <c r="V22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*20</f>
-        <v>43000</v>
-      </c>
-      <c r="W22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*21</f>
-        <v>45000</v>
-      </c>
-      <c r="X22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*22</f>
-        <v>47000</v>
-      </c>
-      <c r="Y22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*23</f>
-        <v>49000</v>
-      </c>
-      <c r="Z22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*24</f>
-        <v>51000</v>
-      </c>
-      <c r="AA22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*25</f>
-        <v>53000</v>
-      </c>
-      <c r="AB22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*26</f>
-        <v>55000</v>
-      </c>
-      <c r="AC22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*27</f>
-        <v>57000</v>
-      </c>
-      <c r="AD22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*28</f>
-        <v>59000</v>
-      </c>
-      <c r="AE22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*29</f>
-        <v>61000</v>
-      </c>
-      <c r="AF22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*30</f>
-        <v>63000</v>
-      </c>
-      <c r="AG22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*31</f>
-        <v>65000</v>
-      </c>
-      <c r="AH22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*32</f>
-        <v>67000</v>
-      </c>
-      <c r="AI22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*33</f>
-        <v>69000</v>
-      </c>
-      <c r="AJ22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*34</f>
-        <v>71000</v>
-      </c>
-      <c r="AK22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*35</f>
-        <v>73000</v>
-      </c>
-      <c r="AL22" s="49" t="n">
-        <f aca="false">前提条件!$C$45+前提条件!$C$46*36</f>
-        <v>75000</v>
-      </c>
+      <c r="B22" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14"/>
+      <c r="AD22" s="14"/>
+      <c r="AE22" s="14"/>
+      <c r="AF22" s="14"/>
+      <c r="AG22" s="14"/>
+      <c r="AH22" s="14"/>
+      <c r="AI22" s="14"/>
+      <c r="AJ22" s="14"/>
+      <c r="AK22" s="14"/>
+      <c r="AL22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C23" s="49" t="n">
-        <f aca="false">C22*前提条件!$C$44</f>
-        <v>210</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*1</f>
+        <v>5000</v>
       </c>
       <c r="D23" s="49" t="n">
-        <f aca="false">D22*前提条件!$C$44</f>
-        <v>294</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*2</f>
+        <v>7000</v>
       </c>
       <c r="E23" s="49" t="n">
-        <f aca="false">E22*前提条件!$C$44</f>
-        <v>378</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*3</f>
+        <v>9000</v>
       </c>
       <c r="F23" s="49" t="n">
-        <f aca="false">F22*前提条件!$C$44</f>
-        <v>462</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*4</f>
+        <v>11000</v>
       </c>
       <c r="G23" s="49" t="n">
-        <f aca="false">G22*前提条件!$C$44</f>
-        <v>546</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*5</f>
+        <v>13000</v>
       </c>
       <c r="H23" s="49" t="n">
-        <f aca="false">H22*前提条件!$C$44</f>
-        <v>630</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*6</f>
+        <v>15000</v>
       </c>
       <c r="I23" s="49" t="n">
-        <f aca="false">I22*前提条件!$C$44</f>
-        <v>714</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*7</f>
+        <v>17000</v>
       </c>
       <c r="J23" s="49" t="n">
-        <f aca="false">J22*前提条件!$C$44</f>
-        <v>798</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*8</f>
+        <v>19000</v>
       </c>
       <c r="K23" s="49" t="n">
-        <f aca="false">K22*前提条件!$C$44</f>
-        <v>882</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*9</f>
+        <v>21000</v>
       </c>
       <c r="L23" s="49" t="n">
-        <f aca="false">L22*前提条件!$C$44</f>
-        <v>966</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*10</f>
+        <v>23000</v>
       </c>
       <c r="M23" s="49" t="n">
-        <f aca="false">M22*前提条件!$C$44</f>
-        <v>1050</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*11</f>
+        <v>25000</v>
       </c>
       <c r="N23" s="49" t="n">
-        <f aca="false">N22*前提条件!$C$44</f>
-        <v>1134</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*12</f>
+        <v>27000</v>
       </c>
       <c r="O23" s="49" t="n">
-        <f aca="false">O22*前提条件!$C$44</f>
-        <v>1218</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*13</f>
+        <v>29000</v>
       </c>
       <c r="P23" s="49" t="n">
-        <f aca="false">P22*前提条件!$C$44</f>
-        <v>1302</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*14</f>
+        <v>31000</v>
       </c>
       <c r="Q23" s="49" t="n">
-        <f aca="false">Q22*前提条件!$C$44</f>
-        <v>1386</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*15</f>
+        <v>33000</v>
       </c>
       <c r="R23" s="49" t="n">
-        <f aca="false">R22*前提条件!$C$44</f>
-        <v>1470</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*16</f>
+        <v>35000</v>
       </c>
       <c r="S23" s="49" t="n">
-        <f aca="false">S22*前提条件!$C$44</f>
-        <v>1554</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*17</f>
+        <v>37000</v>
       </c>
       <c r="T23" s="49" t="n">
-        <f aca="false">T22*前提条件!$C$44</f>
-        <v>1638</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*18</f>
+        <v>39000</v>
       </c>
       <c r="U23" s="49" t="n">
-        <f aca="false">U22*前提条件!$C$44</f>
-        <v>1722</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*19</f>
+        <v>41000</v>
       </c>
       <c r="V23" s="49" t="n">
-        <f aca="false">V22*前提条件!$C$44</f>
-        <v>1806</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*20</f>
+        <v>43000</v>
       </c>
       <c r="W23" s="49" t="n">
-        <f aca="false">W22*前提条件!$C$44</f>
-        <v>1890</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*21</f>
+        <v>45000</v>
       </c>
       <c r="X23" s="49" t="n">
-        <f aca="false">X22*前提条件!$C$44</f>
-        <v>1974</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*22</f>
+        <v>47000</v>
       </c>
       <c r="Y23" s="49" t="n">
-        <f aca="false">Y22*前提条件!$C$44</f>
-        <v>2058</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*23</f>
+        <v>49000</v>
       </c>
       <c r="Z23" s="49" t="n">
-        <f aca="false">Z22*前提条件!$C$44</f>
-        <v>2142</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*24</f>
+        <v>51000</v>
       </c>
       <c r="AA23" s="49" t="n">
-        <f aca="false">AA22*前提条件!$C$44</f>
-        <v>2226</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*25</f>
+        <v>53000</v>
       </c>
       <c r="AB23" s="49" t="n">
-        <f aca="false">AB22*前提条件!$C$44</f>
-        <v>2310</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*26</f>
+        <v>55000</v>
       </c>
       <c r="AC23" s="49" t="n">
-        <f aca="false">AC22*前提条件!$C$44</f>
-        <v>2394</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*27</f>
+        <v>57000</v>
       </c>
       <c r="AD23" s="49" t="n">
-        <f aca="false">AD22*前提条件!$C$44</f>
-        <v>2478</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*28</f>
+        <v>59000</v>
       </c>
       <c r="AE23" s="49" t="n">
-        <f aca="false">AE22*前提条件!$C$44</f>
-        <v>2562</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*29</f>
+        <v>61000</v>
       </c>
       <c r="AF23" s="49" t="n">
-        <f aca="false">AF22*前提条件!$C$44</f>
-        <v>2646</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*30</f>
+        <v>63000</v>
       </c>
       <c r="AG23" s="49" t="n">
-        <f aca="false">AG22*前提条件!$C$44</f>
-        <v>2730</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*31</f>
+        <v>65000</v>
       </c>
       <c r="AH23" s="49" t="n">
-        <f aca="false">AH22*前提条件!$C$44</f>
-        <v>2814</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*32</f>
+        <v>67000</v>
       </c>
       <c r="AI23" s="49" t="n">
-        <f aca="false">AI22*前提条件!$C$44</f>
-        <v>2898</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*33</f>
+        <v>69000</v>
       </c>
       <c r="AJ23" s="49" t="n">
-        <f aca="false">AJ22*前提条件!$C$44</f>
-        <v>2982</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*34</f>
+        <v>71000</v>
       </c>
       <c r="AK23" s="49" t="n">
-        <f aca="false">AK22*前提条件!$C$44</f>
-        <v>3066</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*35</f>
+        <v>73000</v>
       </c>
       <c r="AL23" s="49" t="n">
-        <f aca="false">AL22*前提条件!$C$44</f>
-        <v>3150</v>
+        <f aca="false">前提条件!$C$56+前提条件!$C$57*36</f>
+        <v>75000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C24" s="52" t="n">
-        <f aca="false">-(C23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-24668.25</v>
-      </c>
-      <c r="D24" s="52" t="n">
-        <f aca="false">-(D23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-24863.55</v>
-      </c>
-      <c r="E24" s="52" t="n">
-        <f aca="false">-(E23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-25058.85</v>
-      </c>
-      <c r="F24" s="52" t="n">
-        <f aca="false">-(F23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-25254.15</v>
-      </c>
-      <c r="G24" s="52" t="n">
-        <f aca="false">-(G23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-25449.45</v>
-      </c>
-      <c r="H24" s="52" t="n">
-        <f aca="false">-(H23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-25644.75</v>
-      </c>
-      <c r="I24" s="52" t="n">
-        <f aca="false">-(I23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-25840.05</v>
-      </c>
-      <c r="J24" s="52" t="n">
-        <f aca="false">-(J23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-26035.35</v>
-      </c>
-      <c r="K24" s="52" t="n">
-        <f aca="false">-(K23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-26230.65</v>
-      </c>
-      <c r="L24" s="52" t="n">
-        <f aca="false">-(L23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-26425.95</v>
-      </c>
-      <c r="M24" s="52" t="n">
-        <f aca="false">-(M23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-26621.25</v>
-      </c>
-      <c r="N24" s="52" t="n">
-        <f aca="false">-(N23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-26816.55</v>
-      </c>
-      <c r="O24" s="52" t="n">
-        <f aca="false">-(O23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-27011.85</v>
-      </c>
-      <c r="P24" s="52" t="n">
-        <f aca="false">-(P23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-27207.15</v>
-      </c>
-      <c r="Q24" s="52" t="n">
-        <f aca="false">-(Q23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-27402.45</v>
-      </c>
-      <c r="R24" s="52" t="n">
-        <f aca="false">-(R23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-27597.75</v>
-      </c>
-      <c r="S24" s="52" t="n">
-        <f aca="false">-(S23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-27793.05</v>
-      </c>
-      <c r="T24" s="52" t="n">
-        <f aca="false">-(T23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-27988.35</v>
-      </c>
-      <c r="U24" s="52" t="n">
-        <f aca="false">-(U23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-28183.65</v>
-      </c>
-      <c r="V24" s="52" t="n">
-        <f aca="false">-(V23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-28378.95</v>
-      </c>
-      <c r="W24" s="52" t="n">
-        <f aca="false">-(W23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-28574.25</v>
-      </c>
-      <c r="X24" s="52" t="n">
-        <f aca="false">-(X23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-28769.55</v>
-      </c>
-      <c r="Y24" s="52" t="n">
-        <f aca="false">-(Y23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-28964.85</v>
-      </c>
-      <c r="Z24" s="52" t="n">
-        <f aca="false">-(Z23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-29160.15</v>
-      </c>
-      <c r="AA24" s="52" t="n">
-        <f aca="false">-(AA23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-29355.45</v>
-      </c>
-      <c r="AB24" s="52" t="n">
-        <f aca="false">-(AB23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-29550.75</v>
-      </c>
-      <c r="AC24" s="52" t="n">
-        <f aca="false">-(AC23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-29746.05</v>
-      </c>
-      <c r="AD24" s="52" t="n">
-        <f aca="false">-(AD23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-29941.35</v>
-      </c>
-      <c r="AE24" s="52" t="n">
-        <f aca="false">-(AE23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-30136.65</v>
-      </c>
-      <c r="AF24" s="52" t="n">
-        <f aca="false">-(AF23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-30331.95</v>
-      </c>
-      <c r="AG24" s="52" t="n">
-        <f aca="false">-(AG23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-30527.25</v>
-      </c>
-      <c r="AH24" s="52" t="n">
-        <f aca="false">-(AH23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-30722.55</v>
-      </c>
-      <c r="AI24" s="52" t="n">
-        <f aca="false">-(AI23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-30917.85</v>
-      </c>
-      <c r="AJ24" s="52" t="n">
-        <f aca="false">-(AJ23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-31113.15</v>
-      </c>
-      <c r="AK24" s="52" t="n">
-        <f aca="false">-(AK23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-31308.45</v>
-      </c>
-      <c r="AL24" s="52" t="n">
-        <f aca="false">-(AL23*前提条件!$C$43+前提条件!$C$47+前提条件!$C$46/1000*前提条件!$C$48)*前提条件!$C$42</f>
-        <v>-31503.75</v>
+        <v>188</v>
+      </c>
+      <c r="C24" s="49" t="n">
+        <f aca="false">C23*前提条件!$C$55</f>
+        <v>210</v>
+      </c>
+      <c r="D24" s="49" t="n">
+        <f aca="false">D23*前提条件!$C$55</f>
+        <v>294</v>
+      </c>
+      <c r="E24" s="49" t="n">
+        <f aca="false">E23*前提条件!$C$55</f>
+        <v>378</v>
+      </c>
+      <c r="F24" s="49" t="n">
+        <f aca="false">F23*前提条件!$C$55</f>
+        <v>462</v>
+      </c>
+      <c r="G24" s="49" t="n">
+        <f aca="false">G23*前提条件!$C$55</f>
+        <v>546</v>
+      </c>
+      <c r="H24" s="49" t="n">
+        <f aca="false">H23*前提条件!$C$55</f>
+        <v>630</v>
+      </c>
+      <c r="I24" s="49" t="n">
+        <f aca="false">I23*前提条件!$C$55</f>
+        <v>714</v>
+      </c>
+      <c r="J24" s="49" t="n">
+        <f aca="false">J23*前提条件!$C$55</f>
+        <v>798</v>
+      </c>
+      <c r="K24" s="49" t="n">
+        <f aca="false">K23*前提条件!$C$55</f>
+        <v>882</v>
+      </c>
+      <c r="L24" s="49" t="n">
+        <f aca="false">L23*前提条件!$C$55</f>
+        <v>966</v>
+      </c>
+      <c r="M24" s="49" t="n">
+        <f aca="false">M23*前提条件!$C$55</f>
+        <v>1050</v>
+      </c>
+      <c r="N24" s="49" t="n">
+        <f aca="false">N23*前提条件!$C$55</f>
+        <v>1134</v>
+      </c>
+      <c r="O24" s="49" t="n">
+        <f aca="false">O23*前提条件!$C$55</f>
+        <v>1218</v>
+      </c>
+      <c r="P24" s="49" t="n">
+        <f aca="false">P23*前提条件!$C$55</f>
+        <v>1302</v>
+      </c>
+      <c r="Q24" s="49" t="n">
+        <f aca="false">Q23*前提条件!$C$55</f>
+        <v>1386</v>
+      </c>
+      <c r="R24" s="49" t="n">
+        <f aca="false">R23*前提条件!$C$55</f>
+        <v>1470</v>
+      </c>
+      <c r="S24" s="49" t="n">
+        <f aca="false">S23*前提条件!$C$55</f>
+        <v>1554</v>
+      </c>
+      <c r="T24" s="49" t="n">
+        <f aca="false">T23*前提条件!$C$55</f>
+        <v>1638</v>
+      </c>
+      <c r="U24" s="49" t="n">
+        <f aca="false">U23*前提条件!$C$55</f>
+        <v>1722</v>
+      </c>
+      <c r="V24" s="49" t="n">
+        <f aca="false">V23*前提条件!$C$55</f>
+        <v>1806</v>
+      </c>
+      <c r="W24" s="49" t="n">
+        <f aca="false">W23*前提条件!$C$55</f>
+        <v>1890</v>
+      </c>
+      <c r="X24" s="49" t="n">
+        <f aca="false">X23*前提条件!$C$55</f>
+        <v>1974</v>
+      </c>
+      <c r="Y24" s="49" t="n">
+        <f aca="false">Y23*前提条件!$C$55</f>
+        <v>2058</v>
+      </c>
+      <c r="Z24" s="49" t="n">
+        <f aca="false">Z23*前提条件!$C$55</f>
+        <v>2142</v>
+      </c>
+      <c r="AA24" s="49" t="n">
+        <f aca="false">AA23*前提条件!$C$55</f>
+        <v>2226</v>
+      </c>
+      <c r="AB24" s="49" t="n">
+        <f aca="false">AB23*前提条件!$C$55</f>
+        <v>2310</v>
+      </c>
+      <c r="AC24" s="49" t="n">
+        <f aca="false">AC23*前提条件!$C$55</f>
+        <v>2394</v>
+      </c>
+      <c r="AD24" s="49" t="n">
+        <f aca="false">AD23*前提条件!$C$55</f>
+        <v>2478</v>
+      </c>
+      <c r="AE24" s="49" t="n">
+        <f aca="false">AE23*前提条件!$C$55</f>
+        <v>2562</v>
+      </c>
+      <c r="AF24" s="49" t="n">
+        <f aca="false">AF23*前提条件!$C$55</f>
+        <v>2646</v>
+      </c>
+      <c r="AG24" s="49" t="n">
+        <f aca="false">AG23*前提条件!$C$55</f>
+        <v>2730</v>
+      </c>
+      <c r="AH24" s="49" t="n">
+        <f aca="false">AH23*前提条件!$C$55</f>
+        <v>2814</v>
+      </c>
+      <c r="AI24" s="49" t="n">
+        <f aca="false">AI23*前提条件!$C$55</f>
+        <v>2898</v>
+      </c>
+      <c r="AJ24" s="49" t="n">
+        <f aca="false">AJ23*前提条件!$C$55</f>
+        <v>2982</v>
+      </c>
+      <c r="AK24" s="49" t="n">
+        <f aca="false">AK23*前提条件!$C$55</f>
+        <v>3066</v>
+      </c>
+      <c r="AL24" s="49" t="n">
+        <f aca="false">AL23*前提条件!$C$55</f>
+        <v>3150</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(C24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-24668.25</v>
       </c>
       <c r="D25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(D24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-24863.55</v>
       </c>
       <c r="E25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(E24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-25058.85</v>
       </c>
       <c r="F25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(F24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-25254.15</v>
       </c>
       <c r="G25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(G24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-25449.45</v>
       </c>
       <c r="H25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(H24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-25644.75</v>
       </c>
       <c r="I25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(I24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-25840.05</v>
       </c>
       <c r="J25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(J24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-26035.35</v>
       </c>
       <c r="K25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(K24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-26230.65</v>
       </c>
       <c r="L25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(L24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-26425.95</v>
       </c>
       <c r="M25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(M24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-26621.25</v>
       </c>
       <c r="N25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(N24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-26816.55</v>
       </c>
       <c r="O25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(O24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-27011.85</v>
       </c>
       <c r="P25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(P24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-27207.15</v>
       </c>
       <c r="Q25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(Q24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-27402.45</v>
       </c>
       <c r="R25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(R24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-27597.75</v>
       </c>
       <c r="S25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(S24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-27793.05</v>
       </c>
       <c r="T25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(T24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-27988.35</v>
       </c>
       <c r="U25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(U24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-28183.65</v>
       </c>
       <c r="V25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(V24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-28378.95</v>
       </c>
       <c r="W25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(W24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-28574.25</v>
       </c>
       <c r="X25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(X24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-28769.55</v>
       </c>
       <c r="Y25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(Y24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-28964.85</v>
       </c>
       <c r="Z25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(Z24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-29160.15</v>
       </c>
       <c r="AA25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AA24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-29355.45</v>
       </c>
       <c r="AB25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AB24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-29550.75</v>
       </c>
       <c r="AC25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AC24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-29746.05</v>
       </c>
       <c r="AD25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AD24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-29941.35</v>
       </c>
       <c r="AE25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AE24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-30136.65</v>
       </c>
       <c r="AF25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AF24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-30331.95</v>
       </c>
       <c r="AG25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AG24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-30527.25</v>
       </c>
       <c r="AH25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AH24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-30722.55</v>
       </c>
       <c r="AI25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AI24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-30917.85</v>
       </c>
       <c r="AJ25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AJ24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-31113.15</v>
       </c>
       <c r="AK25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AK24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-31308.45</v>
       </c>
       <c r="AL25" s="52" t="n">
-        <f aca="false">-(前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37)</f>
-        <v>-2400000</v>
+        <f aca="false">-(AL24*前提条件!$C$54+前提条件!$C$58+前提条件!$C$57/1000*前提条件!$C$59)*前提条件!$C$53</f>
+        <v>-31503.75</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="D26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="E26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="F26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="G26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="H26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="I26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="J26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="K26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="L26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="M26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="N26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="O26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="P26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="Q26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="R26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="S26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="T26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="U26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="V26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="W26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="X26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="Y26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="Z26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AA26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AB26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AC26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AD26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AE26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AF26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AG26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AH26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AI26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AJ26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AK26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
       <c r="AL26" s="52" t="n">
-        <f aca="false">-(前提条件!$C$38+前提条件!$C$39)</f>
-        <v>-250000</v>
+        <f aca="false">-(前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48)</f>
+        <v>-2400000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C27" s="52" t="n">
-        <f aca="false">-C8*前提条件!$C$27</f>
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="D27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="E27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="F27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="G27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="H27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="I27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="J27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="K27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="L27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="M27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="N27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="O27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="P27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="Q27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="R27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="S27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="T27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="U27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="V27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="W27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="X27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="Y27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="Z27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AA27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AB27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AC27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AD27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AE27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AF27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AG27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AH27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AI27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AJ27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AK27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+      <c r="AL27" s="52" t="n">
+        <f aca="false">-(前提条件!$C$49+前提条件!$C$50)</f>
+        <v>-250000</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" s="52" t="n">
+        <f aca="false">-C8*前提条件!$C$38</f>
         <v>-100000</v>
       </c>
-      <c r="D27" s="52" t="n">
-        <f aca="false">-D8*前提条件!$C$27</f>
+      <c r="D28" s="52" t="n">
+        <f aca="false">-D8*前提条件!$C$38</f>
         <v>-120000</v>
       </c>
-      <c r="E27" s="52" t="n">
-        <f aca="false">-E8*前提条件!$C$27</f>
+      <c r="E28" s="52" t="n">
+        <f aca="false">-E8*前提条件!$C$38</f>
         <v>-140000</v>
       </c>
-      <c r="F27" s="52" t="n">
-        <f aca="false">-F8*前提条件!$C$27</f>
+      <c r="F28" s="52" t="n">
+        <f aca="false">-F8*前提条件!$C$38</f>
         <v>-160000</v>
       </c>
-      <c r="G27" s="52" t="n">
-        <f aca="false">-G8*前提条件!$C$27</f>
+      <c r="G28" s="52" t="n">
+        <f aca="false">-G8*前提条件!$C$38</f>
         <v>-180000</v>
       </c>
-      <c r="H27" s="52" t="n">
-        <f aca="false">-H8*前提条件!$C$27</f>
+      <c r="H28" s="52" t="n">
+        <f aca="false">-H8*前提条件!$C$38</f>
         <v>-200000</v>
       </c>
-      <c r="I27" s="52" t="n">
-        <f aca="false">-I8*前提条件!$C$27</f>
+      <c r="I28" s="52" t="n">
+        <f aca="false">-I8*前提条件!$C$38</f>
         <v>-240000</v>
       </c>
-      <c r="J27" s="52" t="n">
-        <f aca="false">-J8*前提条件!$C$27</f>
+      <c r="J28" s="52" t="n">
+        <f aca="false">-J8*前提条件!$C$38</f>
         <v>-260000</v>
       </c>
-      <c r="K27" s="52" t="n">
-        <f aca="false">-K8*前提条件!$C$27</f>
+      <c r="K28" s="52" t="n">
+        <f aca="false">-K8*前提条件!$C$38</f>
         <v>-300000</v>
       </c>
-      <c r="L27" s="52" t="n">
-        <f aca="false">-L8*前提条件!$C$27</f>
+      <c r="L28" s="52" t="n">
+        <f aca="false">-L8*前提条件!$C$38</f>
         <v>-360000</v>
       </c>
-      <c r="M27" s="52" t="n">
-        <f aca="false">-M8*前提条件!$C$27</f>
+      <c r="M28" s="52" t="n">
+        <f aca="false">-M8*前提条件!$C$38</f>
         <v>-400000</v>
       </c>
-      <c r="N27" s="52" t="n">
-        <f aca="false">-N8*前提条件!$C$27</f>
+      <c r="N28" s="52" t="n">
+        <f aca="false">-N8*前提条件!$C$38</f>
         <v>-460000</v>
       </c>
-      <c r="O27" s="52" t="n">
-        <f aca="false">-O8*前提条件!$C$27</f>
+      <c r="O28" s="52" t="n">
+        <f aca="false">-O8*前提条件!$C$38</f>
         <v>-540000</v>
       </c>
-      <c r="P27" s="52" t="n">
-        <f aca="false">-P8*前提条件!$C$27</f>
+      <c r="P28" s="52" t="n">
+        <f aca="false">-P8*前提条件!$C$38</f>
         <v>-620000</v>
       </c>
-      <c r="Q27" s="52" t="n">
-        <f aca="false">-Q8*前提条件!$C$27</f>
+      <c r="Q28" s="52" t="n">
+        <f aca="false">-Q8*前提条件!$C$38</f>
         <v>-700000</v>
       </c>
-      <c r="R27" s="52" t="n">
-        <f aca="false">-R8*前提条件!$C$27</f>
+      <c r="R28" s="52" t="n">
+        <f aca="false">-R8*前提条件!$C$38</f>
         <v>-820000</v>
       </c>
-      <c r="S27" s="52" t="n">
-        <f aca="false">-S8*前提条件!$C$27</f>
+      <c r="S28" s="52" t="n">
+        <f aca="false">-S8*前提条件!$C$38</f>
         <v>-940000</v>
       </c>
-      <c r="T27" s="52" t="n">
-        <f aca="false">-T8*前提条件!$C$27</f>
+      <c r="T28" s="52" t="n">
+        <f aca="false">-T8*前提条件!$C$38</f>
         <v>-1080000</v>
       </c>
-      <c r="U27" s="52" t="n">
-        <f aca="false">-U8*前提条件!$C$27</f>
+      <c r="U28" s="52" t="n">
+        <f aca="false">-U8*前提条件!$C$38</f>
         <v>-1240000</v>
       </c>
-      <c r="V27" s="52" t="n">
-        <f aca="false">-V8*前提条件!$C$27</f>
+      <c r="V28" s="52" t="n">
+        <f aca="false">-V8*前提条件!$C$38</f>
         <v>-1420000</v>
       </c>
-      <c r="W27" s="52" t="n">
-        <f aca="false">-W8*前提条件!$C$27</f>
+      <c r="W28" s="52" t="n">
+        <f aca="false">-W8*前提条件!$C$38</f>
         <v>-1640000</v>
       </c>
-      <c r="X27" s="52" t="n">
-        <f aca="false">-X8*前提条件!$C$27</f>
+      <c r="X28" s="52" t="n">
+        <f aca="false">-X8*前提条件!$C$38</f>
         <v>-1880000</v>
       </c>
-      <c r="Y27" s="52" t="n">
-        <f aca="false">-Y8*前提条件!$C$27</f>
+      <c r="Y28" s="52" t="n">
+        <f aca="false">-Y8*前提条件!$C$38</f>
         <v>-2160000</v>
       </c>
-      <c r="Z27" s="52" t="n">
-        <f aca="false">-Z8*前提条件!$C$27</f>
+      <c r="Z28" s="52" t="n">
+        <f aca="false">-Z8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AA27" s="52" t="n">
-        <f aca="false">-AA8*前提条件!$C$27</f>
+      <c r="AA28" s="52" t="n">
+        <f aca="false">-AA8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AB27" s="52" t="n">
-        <f aca="false">-AB8*前提条件!$C$27</f>
+      <c r="AB28" s="52" t="n">
+        <f aca="false">-AB8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AC27" s="52" t="n">
-        <f aca="false">-AC8*前提条件!$C$27</f>
+      <c r="AC28" s="52" t="n">
+        <f aca="false">-AC8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AD27" s="52" t="n">
-        <f aca="false">-AD8*前提条件!$C$27</f>
+      <c r="AD28" s="52" t="n">
+        <f aca="false">-AD8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AE27" s="52" t="n">
-        <f aca="false">-AE8*前提条件!$C$27</f>
+      <c r="AE28" s="52" t="n">
+        <f aca="false">-AE8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AF27" s="52" t="n">
-        <f aca="false">-AF8*前提条件!$C$27</f>
+      <c r="AF28" s="52" t="n">
+        <f aca="false">-AF8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AG27" s="52" t="n">
-        <f aca="false">-AG8*前提条件!$C$27</f>
+      <c r="AG28" s="52" t="n">
+        <f aca="false">-AG8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AH27" s="52" t="n">
-        <f aca="false">-AH8*前提条件!$C$27</f>
+      <c r="AH28" s="52" t="n">
+        <f aca="false">-AH8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AI27" s="52" t="n">
-        <f aca="false">-AI8*前提条件!$C$27</f>
+      <c r="AI28" s="52" t="n">
+        <f aca="false">-AI8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AJ27" s="52" t="n">
-        <f aca="false">-AJ8*前提条件!$C$27</f>
+      <c r="AJ28" s="52" t="n">
+        <f aca="false">-AJ8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AK27" s="52" t="n">
-        <f aca="false">-AK8*前提条件!$C$27</f>
+      <c r="AK28" s="52" t="n">
+        <f aca="false">-AK8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
-      <c r="AL27" s="52" t="n">
-        <f aca="false">-AL8*前提条件!$C$27</f>
+      <c r="AL28" s="52" t="n">
+        <f aca="false">-AL8*前提条件!$C$38</f>
         <v>-2400000</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C28" s="53" t="n">
-        <f aca="false">SUM(C24:C27)</f>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29" s="53" t="n">
+        <f aca="false">SUM(C25:C28)</f>
         <v>-2774668.25</v>
       </c>
-      <c r="D28" s="53" t="n">
-        <f aca="false">SUM(D24:D27)</f>
+      <c r="D29" s="53" t="n">
+        <f aca="false">SUM(D25:D28)</f>
         <v>-2794863.55</v>
       </c>
-      <c r="E28" s="53" t="n">
-        <f aca="false">SUM(E24:E27)</f>
+      <c r="E29" s="53" t="n">
+        <f aca="false">SUM(E25:E28)</f>
         <v>-2815058.85</v>
       </c>
-      <c r="F28" s="53" t="n">
-        <f aca="false">SUM(F24:F27)</f>
+      <c r="F29" s="53" t="n">
+        <f aca="false">SUM(F25:F28)</f>
         <v>-2835254.15</v>
       </c>
-      <c r="G28" s="53" t="n">
-        <f aca="false">SUM(G24:G27)</f>
+      <c r="G29" s="53" t="n">
+        <f aca="false">SUM(G25:G28)</f>
         <v>-2855449.45</v>
       </c>
-      <c r="H28" s="53" t="n">
-        <f aca="false">SUM(H24:H27)</f>
+      <c r="H29" s="53" t="n">
+        <f aca="false">SUM(H25:H28)</f>
         <v>-2875644.75</v>
       </c>
-      <c r="I28" s="53" t="n">
-        <f aca="false">SUM(I24:I27)</f>
+      <c r="I29" s="53" t="n">
+        <f aca="false">SUM(I25:I28)</f>
         <v>-2915840.05</v>
       </c>
-      <c r="J28" s="53" t="n">
-        <f aca="false">SUM(J24:J27)</f>
+      <c r="J29" s="53" t="n">
+        <f aca="false">SUM(J25:J28)</f>
         <v>-2936035.35</v>
       </c>
-      <c r="K28" s="53" t="n">
-        <f aca="false">SUM(K24:K27)</f>
+      <c r="K29" s="53" t="n">
+        <f aca="false">SUM(K25:K28)</f>
         <v>-2976230.65</v>
       </c>
-      <c r="L28" s="53" t="n">
-        <f aca="false">SUM(L24:L27)</f>
+      <c r="L29" s="53" t="n">
+        <f aca="false">SUM(L25:L28)</f>
         <v>-3036425.95</v>
       </c>
-      <c r="M28" s="53" t="n">
-        <f aca="false">SUM(M24:M27)</f>
+      <c r="M29" s="53" t="n">
+        <f aca="false">SUM(M25:M28)</f>
         <v>-3076621.25</v>
       </c>
-      <c r="N28" s="53" t="n">
-        <f aca="false">SUM(N24:N27)</f>
+      <c r="N29" s="53" t="n">
+        <f aca="false">SUM(N25:N28)</f>
         <v>-3136816.55</v>
       </c>
-      <c r="O28" s="53" t="n">
-        <f aca="false">SUM(O24:O27)</f>
+      <c r="O29" s="53" t="n">
+        <f aca="false">SUM(O25:O28)</f>
         <v>-3217011.85</v>
       </c>
-      <c r="P28" s="53" t="n">
-        <f aca="false">SUM(P24:P27)</f>
+      <c r="P29" s="53" t="n">
+        <f aca="false">SUM(P25:P28)</f>
         <v>-3297207.15</v>
       </c>
-      <c r="Q28" s="53" t="n">
-        <f aca="false">SUM(Q24:Q27)</f>
+      <c r="Q29" s="53" t="n">
+        <f aca="false">SUM(Q25:Q28)</f>
         <v>-3377402.45</v>
       </c>
-      <c r="R28" s="53" t="n">
-        <f aca="false">SUM(R24:R27)</f>
+      <c r="R29" s="53" t="n">
+        <f aca="false">SUM(R25:R28)</f>
         <v>-3497597.75</v>
       </c>
-      <c r="S28" s="53" t="n">
-        <f aca="false">SUM(S24:S27)</f>
+      <c r="S29" s="53" t="n">
+        <f aca="false">SUM(S25:S28)</f>
         <v>-3617793.05</v>
       </c>
-      <c r="T28" s="53" t="n">
-        <f aca="false">SUM(T24:T27)</f>
+      <c r="T29" s="53" t="n">
+        <f aca="false">SUM(T25:T28)</f>
         <v>-3757988.35</v>
       </c>
-      <c r="U28" s="53" t="n">
-        <f aca="false">SUM(U24:U27)</f>
+      <c r="U29" s="53" t="n">
+        <f aca="false">SUM(U25:U28)</f>
         <v>-3918183.65</v>
       </c>
-      <c r="V28" s="53" t="n">
-        <f aca="false">SUM(V24:V27)</f>
+      <c r="V29" s="53" t="n">
+        <f aca="false">SUM(V25:V28)</f>
         <v>-4098378.95</v>
       </c>
-      <c r="W28" s="53" t="n">
-        <f aca="false">SUM(W24:W27)</f>
+      <c r="W29" s="53" t="n">
+        <f aca="false">SUM(W25:W28)</f>
         <v>-4318574.25</v>
       </c>
-      <c r="X28" s="53" t="n">
-        <f aca="false">SUM(X24:X27)</f>
+      <c r="X29" s="53" t="n">
+        <f aca="false">SUM(X25:X28)</f>
         <v>-4558769.55</v>
       </c>
-      <c r="Y28" s="53" t="n">
-        <f aca="false">SUM(Y24:Y27)</f>
+      <c r="Y29" s="53" t="n">
+        <f aca="false">SUM(Y25:Y28)</f>
         <v>-4838964.85</v>
       </c>
-      <c r="Z28" s="53" t="n">
-        <f aca="false">SUM(Z24:Z27)</f>
+      <c r="Z29" s="53" t="n">
+        <f aca="false">SUM(Z25:Z28)</f>
         <v>-5079160.15</v>
       </c>
-      <c r="AA28" s="53" t="n">
-        <f aca="false">SUM(AA24:AA27)</f>
+      <c r="AA29" s="53" t="n">
+        <f aca="false">SUM(AA25:AA28)</f>
         <v>-5079355.45</v>
       </c>
-      <c r="AB28" s="53" t="n">
-        <f aca="false">SUM(AB24:AB27)</f>
+      <c r="AB29" s="53" t="n">
+        <f aca="false">SUM(AB25:AB28)</f>
         <v>-5079550.75</v>
       </c>
-      <c r="AC28" s="53" t="n">
-        <f aca="false">SUM(AC24:AC27)</f>
+      <c r="AC29" s="53" t="n">
+        <f aca="false">SUM(AC25:AC28)</f>
         <v>-5079746.05</v>
       </c>
-      <c r="AD28" s="53" t="n">
-        <f aca="false">SUM(AD24:AD27)</f>
+      <c r="AD29" s="53" t="n">
+        <f aca="false">SUM(AD25:AD28)</f>
         <v>-5079941.35</v>
       </c>
-      <c r="AE28" s="53" t="n">
-        <f aca="false">SUM(AE24:AE27)</f>
+      <c r="AE29" s="53" t="n">
+        <f aca="false">SUM(AE25:AE28)</f>
         <v>-5080136.65</v>
       </c>
-      <c r="AF28" s="53" t="n">
-        <f aca="false">SUM(AF24:AF27)</f>
+      <c r="AF29" s="53" t="n">
+        <f aca="false">SUM(AF25:AF28)</f>
         <v>-5080331.95</v>
       </c>
-      <c r="AG28" s="53" t="n">
-        <f aca="false">SUM(AG24:AG27)</f>
+      <c r="AG29" s="53" t="n">
+        <f aca="false">SUM(AG25:AG28)</f>
         <v>-5080527.25</v>
       </c>
-      <c r="AH28" s="53" t="n">
-        <f aca="false">SUM(AH24:AH27)</f>
+      <c r="AH29" s="53" t="n">
+        <f aca="false">SUM(AH25:AH28)</f>
         <v>-5080722.55</v>
       </c>
-      <c r="AI28" s="53" t="n">
-        <f aca="false">SUM(AI24:AI27)</f>
+      <c r="AI29" s="53" t="n">
+        <f aca="false">SUM(AI25:AI28)</f>
         <v>-5080917.85</v>
       </c>
-      <c r="AJ28" s="53" t="n">
-        <f aca="false">SUM(AJ24:AJ27)</f>
+      <c r="AJ29" s="53" t="n">
+        <f aca="false">SUM(AJ25:AJ28)</f>
         <v>-5081113.15</v>
       </c>
-      <c r="AK28" s="53" t="n">
-        <f aca="false">SUM(AK24:AK27)</f>
+      <c r="AK29" s="53" t="n">
+        <f aca="false">SUM(AK25:AK28)</f>
         <v>-5081308.45</v>
       </c>
-      <c r="AL28" s="53" t="n">
-        <f aca="false">SUM(AL24:AL27)</f>
+      <c r="AL29" s="53" t="n">
+        <f aca="false">SUM(AL25:AL28)</f>
         <v>-5081503.75</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" s="56" t="n">
-        <f aca="false">C19+C28</f>
-        <v>-2771926.0679</v>
-      </c>
-      <c r="D30" s="56" t="n">
-        <f aca="false">D19+D28</f>
-        <v>-2786088.56728</v>
-      </c>
-      <c r="E30" s="56" t="n">
-        <f aca="false">E19+E28</f>
-        <v>-2799154.19382</v>
-      </c>
-      <c r="F30" s="56" t="n">
-        <f aca="false">F19+F28</f>
-        <v>-2811671.38394</v>
-      </c>
-      <c r="G30" s="56" t="n">
-        <f aca="false">G19+G28</f>
-        <v>-2823640.13764</v>
-      </c>
-      <c r="H30" s="56" t="n">
-        <f aca="false">H19+H28</f>
-        <v>-2834512.0185</v>
-      </c>
-      <c r="I30" s="56" t="n">
-        <f aca="false">I19+I28</f>
-        <v>-2863738.5901</v>
-      </c>
-      <c r="J30" s="56" t="n">
-        <f aca="false">J19+J28</f>
-        <v>-2871868.28886</v>
-      </c>
-      <c r="K30" s="56" t="n">
-        <f aca="false">K19+K28</f>
-        <v>-2898901.11478</v>
-      </c>
-      <c r="L30" s="56" t="n">
-        <f aca="false">L19+L28</f>
-        <v>-2943191.7586</v>
-      </c>
-      <c r="M30" s="56" t="n">
-        <f aca="false">M19+M28</f>
-        <v>-2965288.65674</v>
-      </c>
-      <c r="N30" s="56" t="n">
-        <f aca="false">N19+N28</f>
-        <v>-3005191.8092</v>
-      </c>
-      <c r="O30" s="56" t="n">
-        <f aca="false">O19+O28</f>
-        <v>-3061804.34314</v>
-      </c>
-      <c r="P30" s="56" t="n">
-        <f aca="false">P19+P28</f>
-        <v>-3115126.25856</v>
-      </c>
-      <c r="Q30" s="56" t="n">
-        <f aca="false">Q19+Q28</f>
-        <v>-3164609.11904</v>
-      </c>
-      <c r="R30" s="56" t="n">
-        <f aca="false">R19+R28</f>
-        <v>-3249156.05174</v>
-      </c>
-      <c r="S30" s="56" t="n">
-        <f aca="false">S19+S28</f>
-        <v>-3328218.62024</v>
-      </c>
-      <c r="T30" s="56" t="n">
-        <f aca="false">T19+T28</f>
-        <v>-3421796.82454</v>
-      </c>
-      <c r="U30" s="56" t="n">
-        <f aca="false">U19+U28</f>
-        <v>-3528793.7918</v>
-      </c>
-      <c r="V30" s="56" t="n">
-        <f aca="false">V19+V28</f>
-        <v>-3647564.21276</v>
-      </c>
-      <c r="W30" s="56" t="n">
-        <f aca="false">W19+W28</f>
-        <v>-3797011.21458</v>
-      </c>
-      <c r="X30" s="56" t="n">
-        <f aca="false">X19+X28</f>
-        <v>-3956037.92442</v>
-      </c>
-      <c r="Y30" s="56" t="n">
-        <f aca="false">Y19+Y28</f>
-        <v>-4143547.46944</v>
-      </c>
-      <c r="Z30" s="56" t="n">
-        <f aca="false">Z19+Z28</f>
-        <v>-4279539.84964</v>
-      </c>
-      <c r="AA30" s="56" t="n">
-        <f aca="false">AA19+AA28</f>
-        <v>-4171693.1749</v>
-      </c>
-      <c r="AB30" s="56" t="n">
-        <f aca="false">AB19+AB28</f>
-        <v>-4067137.11868</v>
-      </c>
-      <c r="AC30" s="56" t="n">
-        <f aca="false">AC19+AC28</f>
-        <v>-3965871.68098</v>
-      </c>
-      <c r="AD30" s="56" t="n">
-        <f aca="false">AD19+AD28</f>
-        <v>-3867896.8618</v>
-      </c>
-      <c r="AE30" s="56" t="n">
-        <f aca="false">AE19+AE28</f>
-        <v>-3772664.22472</v>
-      </c>
-      <c r="AF30" s="56" t="n">
-        <f aca="false">AF19+AF28</f>
-        <v>-3680173.76974</v>
-      </c>
-      <c r="AG30" s="56" t="n">
-        <f aca="false">AG19+AG28</f>
-        <v>-3590973.93328</v>
-      </c>
-      <c r="AH30" s="56" t="n">
-        <f aca="false">AH19+AH28</f>
-        <v>-3504516.27892</v>
-      </c>
-      <c r="AI30" s="56" t="n">
-        <f aca="false">AI19+AI28</f>
-        <v>-3420252.37024</v>
-      </c>
-      <c r="AJ30" s="56" t="n">
-        <f aca="false">AJ19+AJ28</f>
-        <v>-3338730.64366</v>
-      </c>
-      <c r="AK30" s="56" t="n">
-        <f aca="false">AK19+AK28</f>
-        <v>-3259951.09918</v>
-      </c>
-      <c r="AL30" s="56" t="n">
-        <f aca="false">AL19+AL28</f>
-        <v>-3183365.30038</v>
-      </c>
-    </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" s="53" t="n">
-        <f aca="false">C30</f>
-        <v>-2771926.0679</v>
-      </c>
-      <c r="D31" s="53" t="n">
-        <f aca="false">C31+D30</f>
-        <v>-5558014.63518</v>
-      </c>
-      <c r="E31" s="53" t="n">
-        <f aca="false">D31+E30</f>
-        <v>-8357168.829</v>
-      </c>
-      <c r="F31" s="53" t="n">
-        <f aca="false">E31+F30</f>
-        <v>-11168840.21294</v>
-      </c>
-      <c r="G31" s="53" t="n">
-        <f aca="false">F31+G30</f>
-        <v>-13992480.35058</v>
-      </c>
-      <c r="H31" s="53" t="n">
-        <f aca="false">G31+H30</f>
-        <v>-16826992.36908</v>
-      </c>
-      <c r="I31" s="53" t="n">
-        <f aca="false">H31+I30</f>
-        <v>-19690730.95918</v>
-      </c>
-      <c r="J31" s="53" t="n">
-        <f aca="false">I31+J30</f>
-        <v>-22562599.24804</v>
-      </c>
-      <c r="K31" s="53" t="n">
-        <f aca="false">J31+K30</f>
-        <v>-25461500.36282</v>
-      </c>
-      <c r="L31" s="53" t="n">
-        <f aca="false">K31+L30</f>
-        <v>-28404692.12142</v>
-      </c>
-      <c r="M31" s="53" t="n">
-        <f aca="false">L31+M30</f>
-        <v>-31369980.77816</v>
-      </c>
-      <c r="N31" s="53" t="n">
-        <f aca="false">M31+N30</f>
-        <v>-34375172.58736</v>
-      </c>
-      <c r="O31" s="53" t="n">
-        <f aca="false">N31+O30</f>
-        <v>-37436976.9305</v>
-      </c>
-      <c r="P31" s="53" t="n">
-        <f aca="false">O31+P30</f>
-        <v>-40552103.18906</v>
-      </c>
-      <c r="Q31" s="53" t="n">
-        <f aca="false">P31+Q30</f>
-        <v>-43716712.3081</v>
-      </c>
-      <c r="R31" s="53" t="n">
-        <f aca="false">Q31+R30</f>
-        <v>-46965868.35984</v>
-      </c>
-      <c r="S31" s="53" t="n">
-        <f aca="false">R31+S30</f>
-        <v>-50294086.98008</v>
-      </c>
-      <c r="T31" s="53" t="n">
-        <f aca="false">S31+T30</f>
-        <v>-53715883.80462</v>
-      </c>
-      <c r="U31" s="53" t="n">
-        <f aca="false">T31+U30</f>
-        <v>-57244677.59642</v>
-      </c>
-      <c r="V31" s="53" t="n">
-        <f aca="false">U31+V30</f>
-        <v>-60892241.80918</v>
-      </c>
-      <c r="W31" s="53" t="n">
-        <f aca="false">V31+W30</f>
-        <v>-64689253.02376</v>
-      </c>
-      <c r="X31" s="53" t="n">
-        <f aca="false">W31+X30</f>
-        <v>-68645290.94818</v>
-      </c>
-      <c r="Y31" s="53" t="n">
-        <f aca="false">X31+Y30</f>
-        <v>-72788838.41762</v>
-      </c>
-      <c r="Z31" s="53" t="n">
-        <f aca="false">Y31+Z30</f>
-        <v>-77068378.26726</v>
-      </c>
-      <c r="AA31" s="53" t="n">
-        <f aca="false">Z31+AA30</f>
-        <v>-81240071.44216</v>
-      </c>
-      <c r="AB31" s="53" t="n">
-        <f aca="false">AA31+AB30</f>
-        <v>-85307208.56084</v>
-      </c>
-      <c r="AC31" s="53" t="n">
-        <f aca="false">AB31+AC30</f>
-        <v>-89273080.24182</v>
-      </c>
-      <c r="AD31" s="53" t="n">
-        <f aca="false">AC31+AD30</f>
-        <v>-93140977.10362</v>
-      </c>
-      <c r="AE31" s="53" t="n">
-        <f aca="false">AD31+AE30</f>
-        <v>-96913641.32834</v>
-      </c>
-      <c r="AF31" s="53" t="n">
-        <f aca="false">AE31+AF30</f>
-        <v>-100593815.09808</v>
-      </c>
-      <c r="AG31" s="53" t="n">
-        <f aca="false">AF31+AG30</f>
-        <v>-104184789.03136</v>
-      </c>
-      <c r="AH31" s="53" t="n">
-        <f aca="false">AG31+AH30</f>
-        <v>-107689305.31028</v>
-      </c>
-      <c r="AI31" s="53" t="n">
-        <f aca="false">AH31+AI30</f>
-        <v>-111109557.68052</v>
-      </c>
-      <c r="AJ31" s="53" t="n">
-        <f aca="false">AI31+AJ30</f>
-        <v>-114448288.32418</v>
-      </c>
-      <c r="AK31" s="53" t="n">
-        <f aca="false">AJ31+AK30</f>
-        <v>-117708239.42336</v>
-      </c>
-      <c r="AL31" s="53" t="n">
-        <f aca="false">AK31+AL30</f>
-        <v>-120891604.72374</v>
+      <c r="B31" s="56" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31" s="57" t="n">
+        <f aca="false">C20+C29</f>
+        <v>-2771178.20005455</v>
+      </c>
+      <c r="D31" s="57" t="n">
+        <f aca="false">D20+D29</f>
+        <v>-2783695.39017455</v>
+      </c>
+      <c r="E31" s="57" t="n">
+        <f aca="false">E20+E29</f>
+        <v>-2794816.56031636</v>
+      </c>
+      <c r="F31" s="57" t="n">
+        <f aca="false">F20+F29</f>
+        <v>-2805239.72046909</v>
+      </c>
+      <c r="G31" s="57" t="n">
+        <f aca="false">G20+G29</f>
+        <v>-2814964.87063273</v>
+      </c>
+      <c r="H31" s="57" t="n">
+        <f aca="false">H20+H29</f>
+        <v>-2823294.00081818</v>
+      </c>
+      <c r="I31" s="57" t="n">
+        <f aca="false">I20+I29</f>
+        <v>-2849529.10103636</v>
+      </c>
+      <c r="J31" s="57" t="n">
+        <f aca="false">J20+J29</f>
+        <v>-2854368.18127636</v>
+      </c>
+      <c r="K31" s="57" t="n">
+        <f aca="false">K20+K29</f>
+        <v>-2877811.24153818</v>
+      </c>
+      <c r="L31" s="57" t="n">
+        <f aca="false">L20+L29</f>
+        <v>-2917764.25185455</v>
+      </c>
+      <c r="M31" s="57" t="n">
+        <f aca="false">M20+M29</f>
+        <v>-2934925.22221455</v>
+      </c>
+      <c r="N31" s="57" t="n">
+        <f aca="false">N20+N29</f>
+        <v>-2969294.15261818</v>
+      </c>
+      <c r="O31" s="57" t="n">
+        <f aca="false">O20+O29</f>
+        <v>-3019475.02308727</v>
+      </c>
+      <c r="P31" s="57" t="n">
+        <f aca="false">P20+P29</f>
+        <v>-3065467.83362182</v>
+      </c>
+      <c r="Q31" s="57" t="n">
+        <f aca="false">Q20+Q29</f>
+        <v>-3106574.57423273</v>
+      </c>
+      <c r="R31" s="57" t="n">
+        <f aca="false">R20+R29</f>
+        <v>-3181399.22494182</v>
+      </c>
+      <c r="S31" s="57" t="n">
+        <f aca="false">S20+S29</f>
+        <v>-3249243.77576</v>
+      </c>
+      <c r="T31" s="57" t="n">
+        <f aca="false">T20+T29</f>
+        <v>-3330108.22668727</v>
+      </c>
+      <c r="U31" s="57" t="n">
+        <f aca="false">U20+U29</f>
+        <v>-3422596.55774545</v>
+      </c>
+      <c r="V31" s="57" t="n">
+        <f aca="false">V20+V29</f>
+        <v>-3524614.73896727</v>
+      </c>
+      <c r="W31" s="57" t="n">
+        <f aca="false">W20+W29</f>
+        <v>-3702181.57177636</v>
+      </c>
+      <c r="X31" s="57" t="n">
+        <f aca="false">X20+X29</f>
+        <v>-3846450.35613273</v>
+      </c>
+      <c r="Y31" s="57" t="n">
+        <f aca="false">Y20+Y29</f>
+        <v>-4017107.94570182</v>
+      </c>
+      <c r="Z31" s="57" t="n">
+        <f aca="false">Z20+Z29</f>
+        <v>-4134154.34048364</v>
+      </c>
+      <c r="AA31" s="57" t="n">
+        <f aca="false">AA20+AA29</f>
+        <v>-4006663.67033636</v>
+      </c>
+      <c r="AB31" s="57" t="n">
+        <f aca="false">AB20+AB29</f>
+        <v>-3883061.91298546</v>
+      </c>
+      <c r="AC31" s="57" t="n">
+        <f aca="false">AC20+AC29</f>
+        <v>-3763349.06843091</v>
+      </c>
+      <c r="AD31" s="57" t="n">
+        <f aca="false">AD20+AD29</f>
+        <v>-3647525.13667273</v>
+      </c>
+      <c r="AE31" s="57" t="n">
+        <f aca="false">AE20+AE29</f>
+        <v>-3534941.96557818</v>
+      </c>
+      <c r="AF31" s="57" t="n">
+        <f aca="false">AF20+AF29</f>
+        <v>-3425599.55514727</v>
+      </c>
+      <c r="AG31" s="57" t="n">
+        <f aca="false">AG20+AG29</f>
+        <v>-3320146.05751273</v>
+      </c>
+      <c r="AH31" s="57" t="n">
+        <f aca="false">AH20+AH29</f>
+        <v>-3217933.32054182</v>
+      </c>
+      <c r="AI31" s="57" t="n">
+        <f aca="false">AI20+AI29</f>
+        <v>-3269282.78117091</v>
+      </c>
+      <c r="AJ31" s="57" t="n">
+        <f aca="false">AJ20+AJ29</f>
+        <v>-3180332.23399273</v>
+      </c>
+      <c r="AK31" s="57" t="n">
+        <f aca="false">AK20+AK29</f>
+        <v>-3094373.15819636</v>
+      </c>
+      <c r="AL31" s="57" t="n">
+        <f aca="false">AL20+AL29</f>
+        <v>-3010807.25950546</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C32" s="52" t="n">
+      <c r="B32" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C32" s="53" t="n">
+        <f aca="false">C31</f>
+        <v>-2771178.20005455</v>
+      </c>
+      <c r="D32" s="53" t="n">
+        <f aca="false">C32+D31</f>
+        <v>-5554873.59022909</v>
+      </c>
+      <c r="E32" s="53" t="n">
+        <f aca="false">D32+E31</f>
+        <v>-8349690.15054545</v>
+      </c>
+      <c r="F32" s="53" t="n">
+        <f aca="false">E32+F31</f>
+        <v>-11154929.8710145</v>
+      </c>
+      <c r="G32" s="53" t="n">
+        <f aca="false">F32+G31</f>
+        <v>-13969894.7416473</v>
+      </c>
+      <c r="H32" s="53" t="n">
+        <f aca="false">G32+H31</f>
+        <v>-16793188.7424655</v>
+      </c>
+      <c r="I32" s="53" t="n">
+        <f aca="false">H32+I31</f>
+        <v>-19642717.8435018</v>
+      </c>
+      <c r="J32" s="53" t="n">
+        <f aca="false">I32+J31</f>
+        <v>-22497086.0247782</v>
+      </c>
+      <c r="K32" s="53" t="n">
+        <f aca="false">J32+K31</f>
+        <v>-25374897.2663164</v>
+      </c>
+      <c r="L32" s="53" t="n">
+        <f aca="false">K32+L31</f>
+        <v>-28292661.5181709</v>
+      </c>
+      <c r="M32" s="53" t="n">
+        <f aca="false">L32+M31</f>
+        <v>-31227586.7403855</v>
+      </c>
+      <c r="N32" s="53" t="n">
+        <f aca="false">M32+N31</f>
+        <v>-34196880.8930036</v>
+      </c>
+      <c r="O32" s="53" t="n">
+        <f aca="false">N32+O31</f>
+        <v>-37216355.9160909</v>
+      </c>
+      <c r="P32" s="53" t="n">
+        <f aca="false">O32+P31</f>
+        <v>-40281823.7497127</v>
+      </c>
+      <c r="Q32" s="53" t="n">
+        <f aca="false">P32+Q31</f>
+        <v>-43388398.3239455</v>
+      </c>
+      <c r="R32" s="53" t="n">
+        <f aca="false">Q32+R31</f>
+        <v>-46569797.5488873</v>
+      </c>
+      <c r="S32" s="53" t="n">
+        <f aca="false">R32+S31</f>
+        <v>-49819041.3246473</v>
+      </c>
+      <c r="T32" s="53" t="n">
+        <f aca="false">S32+T31</f>
+        <v>-53149149.5513345</v>
+      </c>
+      <c r="U32" s="53" t="n">
+        <f aca="false">T32+U31</f>
+        <v>-56571746.10908</v>
+      </c>
+      <c r="V32" s="53" t="n">
+        <f aca="false">U32+V31</f>
+        <v>-60096360.8480473</v>
+      </c>
+      <c r="W32" s="53" t="n">
+        <f aca="false">V32+W31</f>
+        <v>-63798542.4198236</v>
+      </c>
+      <c r="X32" s="53" t="n">
+        <f aca="false">W32+X31</f>
+        <v>-67644992.7759564</v>
+      </c>
+      <c r="Y32" s="53" t="n">
+        <f aca="false">X32+Y31</f>
+        <v>-71662100.7216582</v>
+      </c>
+      <c r="Z32" s="53" t="n">
+        <f aca="false">Y32+Z31</f>
+        <v>-75796255.0621418</v>
+      </c>
+      <c r="AA32" s="53" t="n">
+        <f aca="false">Z32+AA31</f>
+        <v>-79802918.7324782</v>
+      </c>
+      <c r="AB32" s="53" t="n">
+        <f aca="false">AA32+AB31</f>
+        <v>-83685980.6454637</v>
+      </c>
+      <c r="AC32" s="53" t="n">
+        <f aca="false">AB32+AC31</f>
+        <v>-87449329.7138946</v>
+      </c>
+      <c r="AD32" s="53" t="n">
+        <f aca="false">AC32+AD31</f>
+        <v>-91096854.8505673</v>
+      </c>
+      <c r="AE32" s="53" t="n">
+        <f aca="false">AD32+AE31</f>
+        <v>-94631796.8161455</v>
+      </c>
+      <c r="AF32" s="53" t="n">
+        <f aca="false">AE32+AF31</f>
+        <v>-98057396.3712927</v>
+      </c>
+      <c r="AG32" s="53" t="n">
+        <f aca="false">AF32+AG31</f>
+        <v>-101377542.428805</v>
+      </c>
+      <c r="AH32" s="53" t="n">
+        <f aca="false">AG32+AH31</f>
+        <v>-104595475.749347</v>
+      </c>
+      <c r="AI32" s="53" t="n">
+        <f aca="false">AH32+AI31</f>
+        <v>-107864758.530518</v>
+      </c>
+      <c r="AJ32" s="53" t="n">
+        <f aca="false">AI32+AJ31</f>
+        <v>-111045090.764511</v>
+      </c>
+      <c r="AK32" s="53" t="n">
+        <f aca="false">AJ32+AK31</f>
+        <v>-114139463.922707</v>
+      </c>
+      <c r="AL32" s="53" t="n">
+        <f aca="false">AK32+AL31</f>
+        <v>-117150271.182213</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C33" s="52" t="n">
         <f aca="false">C10*単位経済!$E$7</f>
         <v>11421</v>
       </c>
-      <c r="D32" s="52" t="n">
+      <c r="D33" s="52" t="n">
         <f aca="false">D10*単位経済!$E$7</f>
         <v>25126.2</v>
       </c>
-      <c r="E32" s="52" t="n">
+      <c r="E33" s="52" t="n">
         <f aca="false">E10*単位経済!$E$7</f>
         <v>41115.6</v>
       </c>
-      <c r="F32" s="52" t="n">
+      <c r="F33" s="52" t="n">
         <f aca="false">F10*単位経済!$E$7</f>
         <v>57105</v>
       </c>
-      <c r="G32" s="52" t="n">
+      <c r="G33" s="52" t="n">
         <f aca="false">G10*単位経済!$E$7</f>
         <v>75378.6</v>
       </c>
-      <c r="H32" s="52" t="n">
+      <c r="H33" s="52" t="n">
         <f aca="false">H10*単位経済!$E$7</f>
         <v>95936.4</v>
       </c>
-      <c r="I32" s="52" t="n">
+      <c r="I33" s="52" t="n">
         <f aca="false">I10*単位経済!$E$7</f>
         <v>121062.6</v>
       </c>
-      <c r="J32" s="52" t="n">
+      <c r="J33" s="52" t="n">
         <f aca="false">J10*単位経済!$E$7</f>
         <v>146188.8</v>
       </c>
-      <c r="K32" s="52" t="n">
+      <c r="K33" s="52" t="n">
         <f aca="false">K10*単位経済!$E$7</f>
         <v>175883.4</v>
       </c>
-      <c r="L32" s="52" t="n">
+      <c r="L33" s="52" t="n">
         <f aca="false">L10*単位経済!$E$7</f>
         <v>212430.6</v>
       </c>
-      <c r="M32" s="52" t="n">
+      <c r="M33" s="52" t="n">
         <f aca="false">M10*単位経済!$E$7</f>
         <v>251262</v>
       </c>
-      <c r="N32" s="52" t="n">
+      <c r="N33" s="52" t="n">
         <f aca="false">N10*単位経済!$E$7</f>
         <v>296946</v>
       </c>
-      <c r="O32" s="52" t="n">
+      <c r="O33" s="52" t="n">
         <f aca="false">O10*単位経済!$E$7</f>
         <v>349482.6</v>
       </c>
-      <c r="P32" s="52" t="n">
+      <c r="P33" s="52" t="n">
         <f aca="false">P10*単位経済!$E$7</f>
         <v>408871.8</v>
       </c>
-      <c r="Q32" s="52" t="n">
+      <c r="Q33" s="52" t="n">
         <f aca="false">Q10*単位経済!$E$7</f>
         <v>477397.8</v>
       </c>
-      <c r="R32" s="52" t="n">
+      <c r="R33" s="52" t="n">
         <f aca="false">R10*単位経済!$E$7</f>
         <v>557344.8</v>
       </c>
-      <c r="S32" s="52" t="n">
+      <c r="S33" s="52" t="n">
         <f aca="false">S10*単位経済!$E$7</f>
         <v>648712.8</v>
       </c>
-      <c r="T32" s="52" t="n">
+      <c r="T33" s="52" t="n">
         <f aca="false">T10*単位経済!$E$7</f>
         <v>751501.8</v>
       </c>
-      <c r="U32" s="52" t="n">
+      <c r="U33" s="52" t="n">
         <f aca="false">U10*単位経済!$E$7</f>
         <v>870280.2</v>
       </c>
-      <c r="V32" s="52" t="n">
+      <c r="V33" s="52" t="n">
         <f aca="false">V10*単位経済!$E$7</f>
         <v>1007332.2</v>
       </c>
-      <c r="W32" s="52" t="n">
+      <c r="W33" s="52" t="n">
         <f aca="false">W10*単位経済!$E$7</f>
         <v>1164942</v>
       </c>
-      <c r="X32" s="52" t="n">
+      <c r="X33" s="52" t="n">
         <f aca="false">X10*単位経済!$E$7</f>
         <v>1345393.8</v>
       </c>
-      <c r="Y32" s="52" t="n">
+      <c r="Y33" s="52" t="n">
         <f aca="false">Y10*単位経済!$E$7</f>
         <v>1550971.8</v>
       </c>
-      <c r="Z32" s="52" t="n">
+      <c r="Z33" s="52" t="n">
         <f aca="false">Z10*単位経済!$E$7</f>
         <v>1779391.8</v>
       </c>
-      <c r="AA32" s="52" t="n">
+      <c r="AA33" s="52" t="n">
         <f aca="false">AA10*単位経済!$E$7</f>
         <v>2000959.2</v>
       </c>
-      <c r="AB32" s="52" t="n">
+      <c r="AB33" s="52" t="n">
         <f aca="false">AB10*単位経済!$E$7</f>
         <v>2215674</v>
       </c>
-      <c r="AC32" s="52" t="n">
+      <c r="AC33" s="52" t="n">
         <f aca="false">AC10*単位経済!$E$7</f>
         <v>2423536.2</v>
       </c>
-      <c r="AD32" s="52" t="n">
+      <c r="AD33" s="52" t="n">
         <f aca="false">AD10*単位経済!$E$7</f>
         <v>2624545.8</v>
       </c>
-      <c r="AE32" s="52" t="n">
+      <c r="AE33" s="52" t="n">
         <f aca="false">AE10*単位経済!$E$7</f>
         <v>2820987</v>
       </c>
-      <c r="AF32" s="52" t="n">
+      <c r="AF33" s="52" t="n">
         <f aca="false">AF10*単位経済!$E$7</f>
         <v>3010575.6</v>
       </c>
-      <c r="AG32" s="52" t="n">
+      <c r="AG33" s="52" t="n">
         <f aca="false">AG10*単位経済!$E$7</f>
         <v>3193311.6</v>
       </c>
-      <c r="AH32" s="52" t="n">
+      <c r="AH33" s="52" t="n">
         <f aca="false">AH10*単位経済!$E$7</f>
         <v>3371479.2</v>
       </c>
-      <c r="AI32" s="52" t="n">
+      <c r="AI33" s="52" t="n">
         <f aca="false">AI10*単位経済!$E$7</f>
         <v>3545078.4</v>
       </c>
-      <c r="AJ32" s="52" t="n">
+      <c r="AJ33" s="52" t="n">
         <f aca="false">AJ10*単位経済!$E$7</f>
         <v>3711825</v>
       </c>
-      <c r="AK32" s="52" t="n">
+      <c r="AK33" s="52" t="n">
         <f aca="false">AK10*単位経済!$E$7</f>
         <v>3874003.2</v>
       </c>
-      <c r="AL32" s="52" t="n">
+      <c r="AL33" s="52" t="n">
         <f aca="false">AL10*単位経済!$E$7</f>
         <v>4031613</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C33" s="52" t="n">
-        <f aca="false">C32*12</f>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" s="52" t="n">
+        <f aca="false">C33*12</f>
         <v>137052</v>
       </c>
-      <c r="D33" s="52" t="n">
-        <f aca="false">D32*12</f>
+      <c r="D34" s="52" t="n">
+        <f aca="false">D33*12</f>
         <v>301514.4</v>
       </c>
-      <c r="E33" s="52" t="n">
-        <f aca="false">E32*12</f>
+      <c r="E34" s="52" t="n">
+        <f aca="false">E33*12</f>
         <v>493387.2</v>
       </c>
-      <c r="F33" s="52" t="n">
-        <f aca="false">F32*12</f>
+      <c r="F34" s="52" t="n">
+        <f aca="false">F33*12</f>
         <v>685260</v>
       </c>
-      <c r="G33" s="52" t="n">
-        <f aca="false">G32*12</f>
+      <c r="G34" s="52" t="n">
+        <f aca="false">G33*12</f>
         <v>904543.2</v>
       </c>
-      <c r="H33" s="52" t="n">
-        <f aca="false">H32*12</f>
+      <c r="H34" s="52" t="n">
+        <f aca="false">H33*12</f>
         <v>1151236.8</v>
       </c>
-      <c r="I33" s="52" t="n">
-        <f aca="false">I32*12</f>
+      <c r="I34" s="52" t="n">
+        <f aca="false">I33*12</f>
         <v>1452751.2</v>
       </c>
-      <c r="J33" s="52" t="n">
-        <f aca="false">J32*12</f>
+      <c r="J34" s="52" t="n">
+        <f aca="false">J33*12</f>
         <v>1754265.6</v>
       </c>
-      <c r="K33" s="52" t="n">
-        <f aca="false">K32*12</f>
+      <c r="K34" s="52" t="n">
+        <f aca="false">K33*12</f>
         <v>2110600.8</v>
       </c>
-      <c r="L33" s="52" t="n">
-        <f aca="false">L32*12</f>
+      <c r="L34" s="52" t="n">
+        <f aca="false">L33*12</f>
         <v>2549167.2</v>
       </c>
-      <c r="M33" s="52" t="n">
-        <f aca="false">M32*12</f>
+      <c r="M34" s="52" t="n">
+        <f aca="false">M33*12</f>
         <v>3015144</v>
       </c>
-      <c r="N33" s="52" t="n">
-        <f aca="false">N32*12</f>
+      <c r="N34" s="52" t="n">
+        <f aca="false">N33*12</f>
         <v>3563352</v>
       </c>
-      <c r="O33" s="52" t="n">
-        <f aca="false">O32*12</f>
+      <c r="O34" s="52" t="n">
+        <f aca="false">O33*12</f>
         <v>4193791.2</v>
       </c>
-      <c r="P33" s="52" t="n">
-        <f aca="false">P32*12</f>
+      <c r="P34" s="52" t="n">
+        <f aca="false">P33*12</f>
         <v>4906461.6</v>
       </c>
-      <c r="Q33" s="52" t="n">
-        <f aca="false">Q32*12</f>
+      <c r="Q34" s="52" t="n">
+        <f aca="false">Q33*12</f>
         <v>5728773.6</v>
       </c>
-      <c r="R33" s="52" t="n">
-        <f aca="false">R32*12</f>
+      <c r="R34" s="52" t="n">
+        <f aca="false">R33*12</f>
         <v>6688137.6</v>
       </c>
-      <c r="S33" s="52" t="n">
-        <f aca="false">S32*12</f>
+      <c r="S34" s="52" t="n">
+        <f aca="false">S33*12</f>
         <v>7784553.6</v>
       </c>
-      <c r="T33" s="52" t="n">
-        <f aca="false">T32*12</f>
+      <c r="T34" s="52" t="n">
+        <f aca="false">T33*12</f>
         <v>9018021.6</v>
       </c>
-      <c r="U33" s="52" t="n">
-        <f aca="false">U32*12</f>
+      <c r="U34" s="52" t="n">
+        <f aca="false">U33*12</f>
         <v>10443362.4</v>
       </c>
-      <c r="V33" s="52" t="n">
-        <f aca="false">V32*12</f>
+      <c r="V34" s="52" t="n">
+        <f aca="false">V33*12</f>
         <v>12087986.4</v>
       </c>
-      <c r="W33" s="52" t="n">
-        <f aca="false">W32*12</f>
+      <c r="W34" s="52" t="n">
+        <f aca="false">W33*12</f>
         <v>13979304</v>
       </c>
-      <c r="X33" s="52" t="n">
-        <f aca="false">X32*12</f>
+      <c r="X34" s="52" t="n">
+        <f aca="false">X33*12</f>
         <v>16144725.6</v>
       </c>
-      <c r="Y33" s="52" t="n">
-        <f aca="false">Y32*12</f>
+      <c r="Y34" s="52" t="n">
+        <f aca="false">Y33*12</f>
         <v>18611661.6</v>
       </c>
-      <c r="Z33" s="52" t="n">
-        <f aca="false">Z32*12</f>
+      <c r="Z34" s="52" t="n">
+        <f aca="false">Z33*12</f>
         <v>21352701.6</v>
       </c>
-      <c r="AA33" s="52" t="n">
-        <f aca="false">AA32*12</f>
+      <c r="AA34" s="52" t="n">
+        <f aca="false">AA33*12</f>
         <v>24011510.4</v>
       </c>
-      <c r="AB33" s="52" t="n">
-        <f aca="false">AB32*12</f>
+      <c r="AB34" s="52" t="n">
+        <f aca="false">AB33*12</f>
         <v>26588088</v>
       </c>
-      <c r="AC33" s="52" t="n">
-        <f aca="false">AC32*12</f>
+      <c r="AC34" s="52" t="n">
+        <f aca="false">AC33*12</f>
         <v>29082434.4</v>
       </c>
-      <c r="AD33" s="52" t="n">
-        <f aca="false">AD32*12</f>
+      <c r="AD34" s="52" t="n">
+        <f aca="false">AD33*12</f>
         <v>31494549.6</v>
       </c>
-      <c r="AE33" s="52" t="n">
-        <f aca="false">AE32*12</f>
+      <c r="AE34" s="52" t="n">
+        <f aca="false">AE33*12</f>
         <v>33851844</v>
       </c>
-      <c r="AF33" s="52" t="n">
-        <f aca="false">AF32*12</f>
+      <c r="AF34" s="52" t="n">
+        <f aca="false">AF33*12</f>
         <v>36126907.2</v>
       </c>
-      <c r="AG33" s="52" t="n">
-        <f aca="false">AG32*12</f>
+      <c r="AG34" s="52" t="n">
+        <f aca="false">AG33*12</f>
         <v>38319739.2</v>
       </c>
-      <c r="AH33" s="52" t="n">
-        <f aca="false">AH32*12</f>
+      <c r="AH34" s="52" t="n">
+        <f aca="false">AH33*12</f>
         <v>40457750.4</v>
       </c>
-      <c r="AI33" s="52" t="n">
-        <f aca="false">AI32*12</f>
+      <c r="AI34" s="52" t="n">
+        <f aca="false">AI33*12</f>
         <v>42540940.8</v>
       </c>
-      <c r="AJ33" s="52" t="n">
-        <f aca="false">AJ32*12</f>
+      <c r="AJ34" s="52" t="n">
+        <f aca="false">AJ33*12</f>
         <v>44541900</v>
       </c>
-      <c r="AK33" s="52" t="n">
-        <f aca="false">AK32*12</f>
+      <c r="AK34" s="52" t="n">
+        <f aca="false">AK33*12</f>
         <v>46488038.4</v>
       </c>
-      <c r="AL33" s="52" t="n">
-        <f aca="false">AL32*12</f>
+      <c r="AL34" s="52" t="n">
+        <f aca="false">AL33*12</f>
         <v>48379356</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C37" s="57" t="n">
+      <c r="B37" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38" s="58" t="n">
         <f aca="false">AL10</f>
         <v>1765</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C38" s="58" t="n">
-        <f aca="false">AL32</f>
-        <v>4031613</v>
-      </c>
-    </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C39" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="C39" s="59" t="n">
         <f aca="false">AL33</f>
+        <v>4031613</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C40" s="59" t="n">
+        <f aca="false">AL34</f>
         <v>48379356</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C40" s="57" t="str">
-        <f aca="false">IFERROR(MATCH(TRUE(),INDEX(C30:AL30&gt;0,0),0),"36ヶ月内に達成せず")</f>
-        <v>36ヶ月内に達成せず</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C41" s="57" t="str">
+        <v>202</v>
+      </c>
+      <c r="C41" s="58" t="str">
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX(C31:AL31&gt;0,0),0),"36ヶ月内に達成せず")</f>
         <v>36ヶ月内に達成せず</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C42" s="58" t="n">
-        <f aca="false">MIN(C31:AL31)</f>
-        <v>-120891604.72374</v>
+        <v>203</v>
+      </c>
+      <c r="C42" s="58" t="str">
+        <f aca="false">IFERROR(MATCH(TRUE(),INDEX(C32:AL32&gt;0,0),0),"36ヶ月内に達成せず")</f>
+        <v>36ヶ月内に達成せず</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="17" t="s">
-        <v>192</v>
+      <c r="B43" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C43" s="59" t="n">
+        <f aca="false">MIN(C32:AL32)</f>
+        <v>-117150271.182213</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="17" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -10839,17 +11393,17 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="10" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="11" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -10861,46 +11415,46 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C6" s="32" t="n">
-        <f aca="false">前提条件!$C$30*前提条件!$C$31+前提条件!$C$32*前提条件!$C$33+前提条件!$C$34*前提条件!$C$35+前提条件!$C$36*前提条件!$C$37</f>
+        <f aca="false">前提条件!$C$41*前提条件!$C$42+前提条件!$C$43*前提条件!$C$44+前提条件!$C$45*前提条件!$C$46+前提条件!$C$47*前提条件!$C$48</f>
         <v>2400000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C7" s="32" t="n">
-        <f aca="false">前提条件!$C$38+前提条件!$C$39</f>
+        <f aca="false">前提条件!$C$49+前提条件!$C$50</f>
         <v>250000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="C8" s="32" t="n">
-        <f aca="false">前提条件!$C$47*前提条件!$C$42</f>
+        <f aca="false">前提条件!$C$58*前提条件!$C$53</f>
         <v>21700</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" s="58" t="n">
+        <v>210</v>
+      </c>
+      <c r="C9" s="59" t="n">
         <f aca="false">SUM(C6:C8)</f>
         <v>2671700</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
@@ -10912,43 +11466,43 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C12" s="59" t="n">
+        <v>213</v>
+      </c>
+      <c r="C12" s="60" t="n">
         <f aca="false">単位経済!$E$12</f>
-        <v>1096.87284</v>
+        <v>1396.01997818182</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="57" t="n">
+        <v>215</v>
+      </c>
+      <c r="C13" s="58" t="n">
         <f aca="false">ROUNDUP(C9/C12,0)</f>
-        <v>2436</v>
+        <v>1914</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="60" t="n">
-        <f aca="false">ROUNDUP((C9+前提条件!$C$23*前提条件!$C$27*0.5)/C12,0)</f>
-        <v>3530</v>
+        <v>217</v>
+      </c>
+      <c r="C14" s="61" t="n">
+        <f aca="false">ROUNDUP((C9+前提条件!$C$34*前提条件!$C$38*0.5)/C12,0)</f>
+        <v>2774</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -10960,162 +11514,162 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="47" t="s">
-        <v>208</v>
-      </c>
-      <c r="C18" s="61" t="n">
+        <v>221</v>
+      </c>
+      <c r="C18" s="62" t="n">
         <v>0.3</v>
       </c>
-      <c r="D18" s="61" t="n">
+      <c r="D18" s="62" t="n">
         <v>0.35</v>
       </c>
-      <c r="E18" s="61" t="n">
+      <c r="E18" s="62" t="n">
         <v>0.4</v>
       </c>
-      <c r="F18" s="61" t="n">
+      <c r="F18" s="62" t="n">
         <v>0.45</v>
       </c>
-      <c r="G18" s="61" t="n">
+      <c r="G18" s="62" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="62" t="n">
+      <c r="B19" s="63" t="n">
         <v>1480</v>
       </c>
-      <c r="C19" s="60" t="n">
+      <c r="C19" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B19*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B19*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-C$18)),0)</f>
         <v>3143</v>
       </c>
-      <c r="D19" s="60" t="n">
+      <c r="D19" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B19*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B19*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-D$18)),0)</f>
         <v>3384</v>
       </c>
-      <c r="E19" s="60" t="n">
+      <c r="E19" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B19*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B19*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-E$18)),0)</f>
         <v>3666</v>
       </c>
-      <c r="F19" s="60" t="n">
+      <c r="F19" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B19*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B19*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-F$18)),0)</f>
         <v>4000</v>
       </c>
-      <c r="G19" s="60" t="n">
+      <c r="G19" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B19*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B19*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-G$18)),0)</f>
         <v>4400</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="62" t="n">
+      <c r="B20" s="63" t="n">
         <v>1980</v>
       </c>
-      <c r="C20" s="60" t="n">
+      <c r="C20" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B20*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B20*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-C$18)),0)</f>
         <v>2349</v>
       </c>
-      <c r="D20" s="60" t="n">
+      <c r="D20" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B20*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B20*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-D$18)),0)</f>
         <v>2530</v>
       </c>
-      <c r="E20" s="60" t="n">
+      <c r="E20" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B20*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B20*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-E$18)),0)</f>
         <v>2741</v>
       </c>
-      <c r="F20" s="60" t="n">
+      <c r="F20" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B20*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B20*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-F$18)),0)</f>
         <v>2990</v>
       </c>
-      <c r="G20" s="60" t="n">
+      <c r="G20" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B20*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B20*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-G$18)),0)</f>
         <v>3289</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="62" t="n">
+      <c r="B21" s="63" t="n">
         <v>2480</v>
       </c>
-      <c r="C21" s="60" t="n">
+      <c r="C21" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B21*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B21*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-C$18)),0)</f>
         <v>1876</v>
       </c>
-      <c r="D21" s="60" t="n">
+      <c r="D21" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B21*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B21*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-D$18)),0)</f>
         <v>2020</v>
       </c>
-      <c r="E21" s="60" t="n">
+      <c r="E21" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B21*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B21*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-E$18)),0)</f>
         <v>2188</v>
       </c>
-      <c r="F21" s="60" t="n">
+      <c r="F21" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B21*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B21*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-F$18)),0)</f>
         <v>2387</v>
       </c>
-      <c r="G21" s="60" t="n">
+      <c r="G21" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B21*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B21*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-G$18)),0)</f>
         <v>2626</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="62" t="n">
+      <c r="B22" s="63" t="n">
         <v>2980</v>
       </c>
-      <c r="C22" s="60" t="n">
+      <c r="C22" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B22*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B22*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-C$18)),0)</f>
         <v>1561</v>
       </c>
-      <c r="D22" s="60" t="n">
+      <c r="D22" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B22*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B22*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-D$18)),0)</f>
         <v>1681</v>
       </c>
-      <c r="E22" s="60" t="n">
+      <c r="E22" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B22*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B22*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-E$18)),0)</f>
         <v>1821</v>
       </c>
-      <c r="F22" s="60" t="n">
+      <c r="F22" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B22*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B22*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-F$18)),0)</f>
         <v>1987</v>
       </c>
-      <c r="G22" s="60" t="n">
+      <c r="G22" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B22*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B22*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-G$18)),0)</f>
         <v>2185</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="62" t="n">
+      <c r="B23" s="63" t="n">
         <v>3480</v>
       </c>
-      <c r="C23" s="60" t="n">
+      <c r="C23" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B23*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B23*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-C$18)),0)</f>
         <v>1337</v>
       </c>
-      <c r="D23" s="60" t="n">
+      <c r="D23" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B23*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B23*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-D$18)),0)</f>
         <v>1440</v>
       </c>
-      <c r="E23" s="60" t="n">
+      <c r="E23" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B23*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B23*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-E$18)),0)</f>
         <v>1560</v>
       </c>
-      <c r="F23" s="60" t="n">
+      <c r="F23" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B23*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B23*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-F$18)),0)</f>
         <v>1701</v>
       </c>
-      <c r="G23" s="60" t="n">
+      <c r="G23" s="61" t="n">
         <f aca="false">ROUNDUP($C$9/(($B23*(1-前提条件!$C$10*前提条件!$C$9)/(1+前提条件!$C$16)-$B23*(1-前提条件!$C$10*前提条件!$C$9)*前提条件!$C$17)*(1-G$18)),0)</f>
         <v>1871</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="24" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
@@ -11127,162 +11681,162 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="17" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="47" t="s">
-        <v>212</v>
-      </c>
-      <c r="C28" s="63" t="n">
+        <v>225</v>
+      </c>
+      <c r="C28" s="64" t="n">
         <v>10000</v>
       </c>
-      <c r="D28" s="63" t="n">
+      <c r="D28" s="64" t="n">
         <v>15000</v>
       </c>
-      <c r="E28" s="63" t="n">
+      <c r="E28" s="64" t="n">
         <v>20000</v>
       </c>
-      <c r="F28" s="63" t="n">
+      <c r="F28" s="64" t="n">
         <v>30000</v>
       </c>
-      <c r="G28" s="63" t="n">
+      <c r="G28" s="64" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="64" t="n">
+      <c r="B29" s="65" t="n">
         <v>0.02</v>
       </c>
-      <c r="C29" s="65" t="n">
+      <c r="C29" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B29)/C$28</f>
-        <v>5.4843642</v>
-      </c>
-      <c r="D29" s="65" t="n">
+        <v>6.98009989090909</v>
+      </c>
+      <c r="D29" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B29)/D$28</f>
-        <v>3.6562428</v>
-      </c>
-      <c r="E29" s="65" t="n">
+        <v>4.65339992727273</v>
+      </c>
+      <c r="E29" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B29)/E$28</f>
-        <v>2.7421821</v>
-      </c>
-      <c r="F29" s="65" t="n">
+        <v>3.49004994545455</v>
+      </c>
+      <c r="F29" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B29)/F$28</f>
-        <v>1.8281214</v>
-      </c>
-      <c r="G29" s="65" t="n">
+        <v>2.32669996363636</v>
+      </c>
+      <c r="G29" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B29)/G$28</f>
-        <v>1.37109105</v>
+        <v>1.74502497272727</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="64" t="n">
+      <c r="B30" s="65" t="n">
         <v>0.025</v>
       </c>
-      <c r="C30" s="65" t="n">
+      <c r="C30" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B30)/C$28</f>
-        <v>4.38749136</v>
-      </c>
-      <c r="D30" s="65" t="n">
+        <v>5.58407991272727</v>
+      </c>
+      <c r="D30" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B30)/D$28</f>
-        <v>2.92499424</v>
-      </c>
-      <c r="E30" s="65" t="n">
+        <v>3.72271994181818</v>
+      </c>
+      <c r="E30" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B30)/E$28</f>
-        <v>2.19374568</v>
-      </c>
-      <c r="F30" s="65" t="n">
+        <v>2.79203995636364</v>
+      </c>
+      <c r="F30" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B30)/F$28</f>
-        <v>1.46249712</v>
-      </c>
-      <c r="G30" s="65" t="n">
+        <v>1.86135997090909</v>
+      </c>
+      <c r="G30" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B30)/G$28</f>
-        <v>1.09687284</v>
+        <v>1.39601997818182</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="64" t="n">
+      <c r="B31" s="65" t="n">
         <v>0.03</v>
       </c>
-      <c r="C31" s="65" t="n">
+      <c r="C31" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B31)/C$28</f>
-        <v>3.6562428</v>
-      </c>
-      <c r="D31" s="65" t="n">
+        <v>4.65339992727273</v>
+      </c>
+      <c r="D31" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B31)/D$28</f>
-        <v>2.4374952</v>
-      </c>
-      <c r="E31" s="65" t="n">
+        <v>3.10226661818182</v>
+      </c>
+      <c r="E31" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B31)/E$28</f>
-        <v>1.8281214</v>
-      </c>
-      <c r="F31" s="65" t="n">
+        <v>2.32669996363636</v>
+      </c>
+      <c r="F31" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B31)/F$28</f>
-        <v>1.2187476</v>
-      </c>
-      <c r="G31" s="65" t="n">
+        <v>1.55113330909091</v>
+      </c>
+      <c r="G31" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B31)/G$28</f>
-        <v>0.9140607</v>
+        <v>1.16334998181818</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="64" t="n">
+      <c r="B32" s="65" t="n">
         <v>0.04</v>
       </c>
-      <c r="C32" s="65" t="n">
+      <c r="C32" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B32)/C$28</f>
-        <v>2.7421821</v>
-      </c>
-      <c r="D32" s="65" t="n">
+        <v>3.49004994545455</v>
+      </c>
+      <c r="D32" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B32)/D$28</f>
-        <v>1.8281214</v>
-      </c>
-      <c r="E32" s="65" t="n">
+        <v>2.32669996363636</v>
+      </c>
+      <c r="E32" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B32)/E$28</f>
-        <v>1.37109105</v>
-      </c>
-      <c r="F32" s="65" t="n">
+        <v>1.74502497272727</v>
+      </c>
+      <c r="F32" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B32)/F$28</f>
-        <v>0.9140607</v>
-      </c>
-      <c r="G32" s="65" t="n">
+        <v>1.16334998181818</v>
+      </c>
+      <c r="G32" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B32)/G$28</f>
-        <v>0.685545525</v>
+        <v>0.872512486363636</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="64" t="n">
+      <c r="B33" s="65" t="n">
         <v>0.05</v>
       </c>
-      <c r="C33" s="65" t="n">
+      <c r="C33" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B33)/C$28</f>
-        <v>2.19374568</v>
-      </c>
-      <c r="D33" s="65" t="n">
+        <v>2.79203995636364</v>
+      </c>
+      <c r="D33" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B33)/D$28</f>
-        <v>1.46249712</v>
-      </c>
-      <c r="E33" s="65" t="n">
+        <v>1.86135997090909</v>
+      </c>
+      <c r="E33" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B33)/E$28</f>
-        <v>1.09687284</v>
-      </c>
-      <c r="F33" s="65" t="n">
+        <v>1.39601997818182</v>
+      </c>
+      <c r="F33" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B33)/F$28</f>
-        <v>0.73124856</v>
-      </c>
-      <c r="G33" s="65" t="n">
+        <v>0.930679985454545</v>
+      </c>
+      <c r="G33" s="66" t="n">
         <f aca="false">(単位経済!$E$12/$B33)/G$28</f>
-        <v>0.54843642</v>
+        <v>0.698009989090909</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="17" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="13" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -11294,112 +11848,112 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="47" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="5" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C38" s="46" t="n">
         <v>700000</v>
       </c>
-      <c r="D38" s="66" t="n">
+      <c r="D38" s="67" t="n">
         <f aca="false">ROUNDUP(C38/$C$12,0)</f>
-        <v>639</v>
+        <v>502</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C39" s="46" t="n">
         <v>1100000</v>
       </c>
-      <c r="D39" s="66" t="n">
+      <c r="D39" s="67" t="n">
         <f aca="false">ROUNDUP(C39/$C$12,0)</f>
-        <v>1003</v>
+        <v>788</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="C40" s="46" t="n">
         <v>1900000</v>
       </c>
-      <c r="D40" s="66" t="n">
+      <c r="D40" s="67" t="n">
         <f aca="false">ROUNDUP(C40/$C$12,0)</f>
-        <v>1733</v>
+        <v>1362</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C41" s="67" t="n">
+        <v>238</v>
+      </c>
+      <c r="C41" s="68" t="n">
         <f aca="false">$C$9</f>
         <v>2671700</v>
       </c>
-      <c r="D41" s="66" t="n">
+      <c r="D41" s="67" t="n">
         <f aca="false">ROUNDUP(C41/$C$12,0)</f>
-        <v>2436</v>
+        <v>1914</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="C42" s="46" t="n">
         <v>4500000</v>
       </c>
-      <c r="D42" s="66" t="n">
+      <c r="D42" s="67" t="n">
         <f aca="false">ROUNDUP(C42/$C$12,0)</f>
-        <v>4103</v>
+        <v>3224</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="3" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="17" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="17" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="17" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -11429,92 +11983,92 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="10" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="68" t="s">
-        <v>235</v>
-      </c>
-      <c r="C5" s="68" t="s">
-        <v>236</v>
-      </c>
-      <c r="D5" s="68" t="s">
-        <v>237</v>
-      </c>
-      <c r="E5" s="69" t="s">
-        <v>238</v>
-      </c>
-      <c r="F5" s="68" t="s">
-        <v>239</v>
-      </c>
-      <c r="G5" s="68" t="s">
-        <v>240</v>
-      </c>
-      <c r="H5" s="68" t="s">
-        <v>43</v>
+      <c r="B5" s="69" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="69" t="s">
+        <v>249</v>
+      </c>
+      <c r="D5" s="69" t="s">
+        <v>250</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>251</v>
+      </c>
+      <c r="F5" s="69" t="s">
+        <v>252</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="H5" s="69" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="C6" s="70" t="n">
+        <v>254</v>
+      </c>
+      <c r="C6" s="71" t="n">
         <f aca="false">前提条件!$C$7</f>
         <v>1980</v>
       </c>
-      <c r="D6" s="71" t="n">
+      <c r="D6" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="72" t="n">
+      <c r="E6" s="73" t="n">
         <f aca="false">C6*36+D6</f>
         <v>71280</v>
       </c>
-      <c r="F6" s="72" t="n">
+      <c r="F6" s="73" t="n">
         <f aca="false">E6-$E$6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="73" t="s">
-        <v>242</v>
-      </c>
-      <c r="H6" s="74" t="s">
-        <v>243</v>
+      <c r="G6" s="74" t="s">
+        <v>255</v>
+      </c>
+      <c r="H6" s="75" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="C7" s="70" t="n">
+        <v>257</v>
+      </c>
+      <c r="C7" s="71" t="n">
         <f aca="false">前提条件!$C$8</f>
         <v>4980</v>
       </c>
-      <c r="D7" s="71" t="n">
+      <c r="D7" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="72" t="n">
+      <c r="E7" s="73" t="n">
         <f aca="false">C7*36+D7</f>
         <v>179280</v>
       </c>
-      <c r="F7" s="72" t="n">
+      <c r="F7" s="73" t="n">
         <f aca="false">E7-$E$6</f>
         <v>108000</v>
       </c>
-      <c r="G7" s="73" t="s">
-        <v>242</v>
-      </c>
-      <c r="H7" s="74" t="s">
-        <v>245</v>
+      <c r="G7" s="74" t="s">
+        <v>255</v>
+      </c>
+      <c r="H7" s="75" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="C8" s="46" t="n">
         <v>6600</v>
@@ -11531,15 +12085,15 @@
         <v>188320</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="C9" s="46" t="n">
         <v>3278</v>
@@ -11556,15 +12110,15 @@
         <v>50028</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C10" s="46" t="n">
         <v>3300</v>
@@ -11581,15 +12135,15 @@
         <v>47520</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C11" s="46" t="n">
         <v>2068</v>
@@ -11606,15 +12160,15 @@
         <v>3168</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C12" s="46" t="n">
         <v>2200</v>
@@ -11631,15 +12185,15 @@
         <v>7920</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C13" s="46" t="n">
         <v>1078</v>
@@ -11656,15 +12210,15 @@
         <v>-32472</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C14" s="46" t="n">
         <v>1089</v>
@@ -11681,15 +12235,15 @@
         <v>-32076</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C15" s="46" t="n">
         <v>690</v>
@@ -11706,15 +12260,15 @@
         <v>-42440</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C16" s="46" t="n">
         <v>550</v>
@@ -11731,25 +12285,25 @@
         <v>-51480</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="24" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="36" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -11760,71 +12314,71 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="24" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C22" s="15" t="n">
         <v>500</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C23" s="32" t="n">
         <f aca="false">E8/36+C22</f>
         <v>7711.11111111111</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C24" s="67" t="n">
+        <v>288</v>
+      </c>
+      <c r="C24" s="68" t="n">
         <f aca="false">前提条件!$C$7</f>
         <v>1980</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C25" s="58" t="n">
+        <v>290</v>
+      </c>
+      <c r="C25" s="59" t="n">
         <f aca="false">C23-C24</f>
         <v>5731.11111111111</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="3" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="17" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="17" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="17" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
